--- a/5_simulation/outputs/tables/supplementary/S11_sector_results.xlsx
+++ b/5_simulation/outputs/tables/supplementary/S11_sector_results.xlsx
@@ -476,19 +476,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7.10467700619</v>
+        <v>8.124242150755023</v>
       </c>
       <c r="E2" t="n">
-        <v>4.05973606189</v>
+        <v>4.240824576844515</v>
       </c>
       <c r="F2" t="n">
-        <v>0.201931026993</v>
+        <v>0.2039710664061395</v>
       </c>
       <c r="G2" t="n">
-        <v>0.202908487935</v>
+        <v>0.2048012086393272</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8827436383043619</v>
+        <v>0.894971927428978</v>
       </c>
     </row>
     <row r="3">
@@ -508,19 +508,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.246861283695</v>
+        <v>-0.5218152663572728</v>
       </c>
       <c r="E3" t="n">
-        <v>1.41746876774</v>
+        <v>1.596435544713071</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00110565488345</v>
+        <v>0.001103144499113312</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000357355257347</v>
+        <v>0.0003562930950074917</v>
       </c>
       <c r="H3" t="n">
-        <v>0.579363439252889</v>
+        <v>0.5767738543340117</v>
       </c>
     </row>
     <row r="4">
@@ -540,19 +540,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-3.24700921278</v>
+        <v>-3.067239399192423</v>
       </c>
       <c r="E4" t="n">
-        <v>3.45017141904</v>
+        <v>3.632967067320036</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00128633532693</v>
+        <v>0.001289107141888093</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0140070246972</v>
+        <v>0.01403057836279584</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.037466446301871</v>
+        <v>-1.028173515141473</v>
       </c>
     </row>
     <row r="5">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.82341923561</v>
+        <v>7.498961523039016</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3097346997</v>
+        <v>1.463451029510177</v>
       </c>
       <c r="F5" t="n">
-        <v>1.10811912175</v>
+        <v>1.113809663925592</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0816873565568</v>
+        <v>0.08221148048223684</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5299505761405809</v>
+        <v>-0.5330987746412608</v>
       </c>
     </row>
     <row r="6">
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.93225465538</v>
+        <v>5.171867402853292</v>
       </c>
       <c r="E6" t="n">
-        <v>4.74412523782</v>
+        <v>4.904248087174201</v>
       </c>
       <c r="F6" t="n">
-        <v>0.200911149006</v>
+        <v>0.203277452598945</v>
       </c>
       <c r="G6" t="n">
-        <v>0.421098677932</v>
+        <v>0.426131827790098</v>
       </c>
       <c r="H6" t="n">
-        <v>1.099339089143547</v>
+        <v>1.108215185315276</v>
       </c>
     </row>
     <row r="7">
@@ -636,19 +636,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.04156133165</v>
+        <v>-1.504798960654485</v>
       </c>
       <c r="E7" t="n">
-        <v>1.66516093934</v>
+        <v>1.78696349035703</v>
       </c>
       <c r="F7" t="n">
-        <v>0.259972209381</v>
+        <v>0.2583027184378602</v>
       </c>
       <c r="G7" t="n">
-        <v>0.586960799535</v>
+        <v>0.5843244094149695</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5363562167016056</v>
+        <v>0.5306777432624088</v>
       </c>
     </row>
     <row r="8">
@@ -668,19 +668,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.90585902616</v>
+        <v>-1.959353234082251</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7007367979</v>
+        <v>1.847697921889768</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0278179594161</v>
+        <v>0.02778891775431549</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0374056106969</v>
+        <v>0.0373879817692061</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.708456635575383</v>
+        <v>-0.71093017294932</v>
       </c>
     </row>
     <row r="9">
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1.31681471975</v>
+        <v>-1.474336593593406</v>
       </c>
       <c r="E9" t="n">
-        <v>1.65213793087</v>
+        <v>1.79671171253899</v>
       </c>
       <c r="F9" t="n">
-        <v>0.118858678545</v>
+        <v>0.1185955530639336</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07707775537019999</v>
+        <v>0.07696237282535125</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1850840873582893</v>
+        <v>0.1779144023466905</v>
       </c>
     </row>
     <row r="10">
@@ -732,19 +732,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.745183676532</v>
+        <v>-0.8434523671233096</v>
       </c>
       <c r="E10" t="n">
-        <v>1.57198203473</v>
+        <v>1.713239945149736</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00348664723738</v>
+        <v>0.003481256458902813</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00335260575803</v>
+        <v>0.003349653409292923</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.004503609537731545</v>
+        <v>-0.007937377645272914</v>
       </c>
     </row>
     <row r="11">
@@ -764,19 +764,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>37.4042045842</v>
+        <v>39.40994766061628</v>
       </c>
       <c r="E11" t="n">
-        <v>21.5259965571</v>
+        <v>21.70750926598553</v>
       </c>
       <c r="F11" t="n">
-        <v>0.481964766881</v>
+        <v>0.4888261791534598</v>
       </c>
       <c r="G11" t="n">
-        <v>0.383317565441</v>
+        <v>0.3889364607537205</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1640857315856947</v>
+        <v>-0.1579375458958587</v>
       </c>
     </row>
     <row r="12">
@@ -796,19 +796,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-6.30699462731</v>
+        <v>-6.221865446240249</v>
       </c>
       <c r="E12" t="n">
-        <v>2.12100343861</v>
+        <v>2.275854851786296</v>
       </c>
       <c r="F12" t="n">
-        <v>0.793406222118</v>
+        <v>0.7937436672380063</v>
       </c>
       <c r="G12" t="n">
-        <v>0.274209995553</v>
+        <v>0.2744743509843067</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2166118555907648</v>
+        <v>-0.2222217893254497</v>
       </c>
     </row>
     <row r="13">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.756396936178</v>
+        <v>-0.9310505790485646</v>
       </c>
       <c r="E13" t="n">
-        <v>1.30207395061</v>
+        <v>1.447001459775255</v>
       </c>
       <c r="F13" t="n">
-        <v>0.123828946961</v>
+        <v>0.1235037699374011</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0289376907749</v>
+        <v>0.02889050644999741</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1753756030559606</v>
+        <v>0.1665266025264955</v>
       </c>
     </row>
     <row r="14">
@@ -860,19 +860,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-2.50502533862</v>
+        <v>-2.55821906171908</v>
       </c>
       <c r="E14" t="n">
-        <v>1.89631841388</v>
+        <v>2.034535387136538</v>
       </c>
       <c r="F14" t="n">
-        <v>0.178709489717</v>
+        <v>0.1784405389147145</v>
       </c>
       <c r="G14" t="n">
-        <v>0.206751952775</v>
+        <v>0.2066651006909482</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5271822770801071</v>
+        <v>-0.5307932022408091</v>
       </c>
     </row>
     <row r="15">
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-1.80715945934</v>
+        <v>-1.801150361993775</v>
       </c>
       <c r="E15" t="n">
-        <v>2.34356924166</v>
+        <v>2.485680962389991</v>
       </c>
       <c r="F15" t="n">
-        <v>0.142461648385</v>
+        <v>0.1423774672567136</v>
       </c>
       <c r="G15" t="n">
-        <v>0.141536737588</v>
+        <v>0.1415610862463884</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.714461037270997</v>
+        <v>-0.716108621317868</v>
       </c>
     </row>
     <row r="16">
@@ -924,19 +924,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-4.05851913607</v>
+        <v>-4.080704262025769</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3950579354</v>
+        <v>1.547316738561388</v>
       </c>
       <c r="F16" t="n">
-        <v>1.36657427918</v>
+        <v>1.365474657284009</v>
       </c>
       <c r="G16" t="n">
-        <v>0.492462459766</v>
+        <v>0.4923806262025446</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.084591945423596</v>
+        <v>-1.089403023764879</v>
       </c>
     </row>
     <row r="17">
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-2.34139745761</v>
+        <v>-2.381120340014942</v>
       </c>
       <c r="E17" t="n">
-        <v>1.41970768563</v>
+        <v>1.558445958122801</v>
       </c>
       <c r="F17" t="n">
-        <v>0.21087359292</v>
+        <v>0.2105801561108153</v>
       </c>
       <c r="G17" t="n">
-        <v>0.274078901231</v>
+        <v>0.2739993088668456</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9973554192183598</v>
+        <v>-1.000237723717678</v>
       </c>
     </row>
     <row r="18">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-2.11403399882</v>
+        <v>-2.250444198274881</v>
       </c>
       <c r="E18" t="n">
-        <v>1.13233806825</v>
+        <v>1.281161953940901</v>
       </c>
       <c r="F18" t="n">
-        <v>0.420672747196</v>
+        <v>0.4195273974695766</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0704708979651</v>
+        <v>0.07038210296345</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8530063483494277</v>
+        <v>-0.8630810258706045</v>
       </c>
     </row>
     <row r="19">
@@ -1020,19 +1020,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-2.7313786255</v>
+        <v>-2.895457806730362</v>
       </c>
       <c r="E19" t="n">
-        <v>1.43685374408</v>
+        <v>1.576834657328563</v>
       </c>
       <c r="F19" t="n">
-        <v>0.392800436764</v>
+        <v>0.3915470175545264</v>
       </c>
       <c r="G19" t="n">
-        <v>0.332193873709</v>
+        <v>0.3316745130957703</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.604203596103059</v>
+        <v>-0.612927794711382</v>
       </c>
     </row>
     <row r="20">
@@ -1052,19 +1052,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-3.31171915087</v>
+        <v>-3.23871005822346</v>
       </c>
       <c r="E20" t="n">
-        <v>1.33710500968</v>
+        <v>1.477976571818673</v>
       </c>
       <c r="F20" t="n">
-        <v>0.625374109217</v>
+        <v>0.6248199307123907</v>
       </c>
       <c r="G20" t="n">
-        <v>0.324113673616</v>
+        <v>0.3244060599491201</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.346753501176168</v>
+        <v>-1.346775268169165</v>
       </c>
     </row>
     <row r="21">
@@ -1084,19 +1084,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-2.89079403828</v>
+        <v>-3.05062821181451</v>
       </c>
       <c r="E21" t="n">
-        <v>1.44425499017</v>
+        <v>1.587184764170479</v>
       </c>
       <c r="F21" t="n">
-        <v>0.869466602242</v>
+        <v>0.8671559204770151</v>
       </c>
       <c r="G21" t="n">
-        <v>0.586012428616</v>
+        <v>0.5851169318055413</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8359820068380985</v>
+        <v>-0.8440628120985338</v>
       </c>
     </row>
     <row r="22">
@@ -1116,19 +1116,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-2.41910504215</v>
+        <v>-2.403809329984363</v>
       </c>
       <c r="E22" t="n">
-        <v>1.27022640357</v>
+        <v>1.410192865221571</v>
       </c>
       <c r="F22" t="n">
-        <v>0.172115717105</v>
+        <v>0.1719062687135161</v>
       </c>
       <c r="G22" t="n">
-        <v>0.138792996064</v>
+        <v>0.1388319057652054</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.376187302893017</v>
+        <v>-1.37768390547266</v>
       </c>
     </row>
     <row r="23">
@@ -1148,19 +1148,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.846056630853</v>
+        <v>-1.314224379057194</v>
       </c>
       <c r="E23" t="n">
-        <v>1.40589697934</v>
+        <v>1.542606265115443</v>
       </c>
       <c r="F23" t="n">
-        <v>0.106949978415</v>
+        <v>0.1063300831872435</v>
       </c>
       <c r="G23" t="n">
-        <v>0.17189789809</v>
+        <v>0.1711070020782832</v>
       </c>
       <c r="H23" t="n">
-        <v>0.07155633523803218</v>
+        <v>0.06356090103849521</v>
       </c>
     </row>
     <row r="24">
@@ -1180,19 +1180,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-2.22764329851</v>
+        <v>-2.065087224496598</v>
       </c>
       <c r="E24" t="n">
-        <v>1.44373715227</v>
+        <v>1.573963588260052</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0347207236214</v>
+        <v>0.0347347005767429</v>
       </c>
       <c r="G24" t="n">
-        <v>0.052079710669</v>
+        <v>0.05217485787225383</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8878159177310163</v>
+        <v>-0.886866966194555</v>
       </c>
     </row>
     <row r="25">
@@ -1212,19 +1212,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1.27072716882</v>
+        <v>1.307617159832697</v>
       </c>
       <c r="E25" t="n">
-        <v>2.07980394819</v>
+        <v>2.237268646577095</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0128765692947</v>
+        <v>0.0128801535755087</v>
       </c>
       <c r="G25" t="n">
-        <v>0.00759827271606</v>
+        <v>0.007601180202293735</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1595482044615126</v>
+        <v>0.1547463961110385</v>
       </c>
     </row>
     <row r="26">
@@ -1244,19 +1244,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.338408134975</v>
+        <v>0.04877341761806431</v>
       </c>
       <c r="E26" t="n">
-        <v>1.56353244414</v>
+        <v>1.683305337777319</v>
       </c>
       <c r="F26" t="n">
-        <v>7.32539684724e-05</v>
+        <v>7.296205473429655e-05</v>
       </c>
       <c r="G26" t="n">
-        <v>5.91023771747e-05</v>
+        <v>5.894570506801052e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>0.550075969889674</v>
+        <v>0.537759824065609</v>
       </c>
     </row>
     <row r="27">
@@ -1276,19 +1276,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-3.16920622325</v>
+        <v>-3.195707773523437</v>
       </c>
       <c r="E27" t="n">
-        <v>1.33278077191</v>
+        <v>1.487324641078525</v>
       </c>
       <c r="F27" t="n">
-        <v>0.212350581108</v>
+        <v>0.2122404925803811</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0210980158039</v>
+        <v>0.02109325260354307</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.7544394996877313</v>
+        <v>-0.7595643518004791</v>
       </c>
     </row>
     <row r="28">
@@ -1308,19 +1308,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-2.15963097556</v>
+        <v>-2.156197377064661</v>
       </c>
       <c r="E28" t="n">
-        <v>1.90401098536</v>
+        <v>2.04342142662457</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06698897843319999</v>
+        <v>0.06696483186878212</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0402243624773</v>
+        <v>0.04023075161040415</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.291831974665136</v>
+        <v>-1.291326309632312</v>
       </c>
     </row>
     <row r="29">
@@ -1340,19 +1340,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-0.494333216203</v>
+        <v>-0.7408011661043101</v>
       </c>
       <c r="E29" t="n">
-        <v>1.52534576911</v>
+        <v>1.679070467245358</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00607863685038</v>
+        <v>0.006062875129917594</v>
       </c>
       <c r="G29" t="n">
-        <v>0.122013512171</v>
+        <v>0.12171444195341</v>
       </c>
       <c r="H29" t="n">
-        <v>0.07881361920145658</v>
+        <v>0.07993601458460287</v>
       </c>
     </row>
     <row r="30">
@@ -1372,19 +1372,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-0.737581033451</v>
+        <v>-0.8245623206549646</v>
       </c>
       <c r="E30" t="n">
-        <v>2.07689090673</v>
+        <v>2.211364132489102</v>
       </c>
       <c r="F30" t="n">
-        <v>0.07042552357450001</v>
+        <v>0.07032697189388878</v>
       </c>
       <c r="G30" t="n">
-        <v>0.458891559517</v>
+        <v>0.4585393638792628</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07674963437984683</v>
+        <v>0.07500616841735752</v>
       </c>
     </row>
     <row r="31">
@@ -1404,19 +1404,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-0.289481068515</v>
+        <v>-0.5206555283119418</v>
       </c>
       <c r="E31" t="n">
-        <v>1.42136793232</v>
+        <v>1.550319561885183</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0121334947571</v>
+        <v>0.01209808169370577</v>
       </c>
       <c r="G31" t="n">
-        <v>0.379637568543</v>
+        <v>0.3788050648475129</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1107907918948214</v>
+        <v>0.1075494599784621</v>
       </c>
     </row>
     <row r="32">
@@ -1436,19 +1436,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-1.67485374465</v>
+        <v>-1.486818750834173</v>
       </c>
       <c r="E32" t="n">
-        <v>3.72100858087</v>
+        <v>3.889619869975758</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0325957634889</v>
+        <v>0.03266155885439204</v>
       </c>
       <c r="G32" t="n">
-        <v>0.467647096949</v>
+        <v>0.4685311571887795</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1216370190361804</v>
+        <v>0.1275750533700437</v>
       </c>
     </row>
     <row r="33">
@@ -1468,19 +1468,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-2.53769943691</v>
+        <v>-2.238184785992325</v>
       </c>
       <c r="E33" t="n">
-        <v>5.16245292933</v>
+        <v>5.318555705893901</v>
       </c>
       <c r="F33" t="n">
-        <v>0.00593746287272</v>
+        <v>0.005954489595380947</v>
       </c>
       <c r="G33" t="n">
-        <v>0.156005072348</v>
+        <v>0.1564875019825095</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2109601498675895</v>
+        <v>-0.2013365679749746</v>
       </c>
     </row>
     <row r="34">
@@ -1500,19 +1500,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-4.55350016406</v>
+        <v>-3.555105811435566</v>
       </c>
       <c r="E34" t="n">
-        <v>5.65266272093</v>
+        <v>5.784162831787865</v>
       </c>
       <c r="F34" t="n">
-        <v>0.018084739643</v>
+        <v>0.01826130861583307</v>
       </c>
       <c r="G34" t="n">
-        <v>0.174927746699</v>
+        <v>0.1767797707134912</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1239965254102415</v>
+        <v>0.1231761473105442</v>
       </c>
     </row>
     <row r="35">
@@ -1532,19 +1532,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-1.96645903982</v>
+        <v>-1.743139190031673</v>
       </c>
       <c r="E35" t="n">
-        <v>2.51267050175</v>
+        <v>2.657319077526132</v>
       </c>
       <c r="F35" t="n">
-        <v>0.08215642019530001</v>
+        <v>0.08231457352723071</v>
       </c>
       <c r="G35" t="n">
-        <v>0.125528232774</v>
+        <v>0.125823875622538</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.05524756213177717</v>
+        <v>-0.05539698395268244</v>
       </c>
     </row>
     <row r="36">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-0.964102643589</v>
+        <v>-1.061395078278993</v>
       </c>
       <c r="E36" t="n">
-        <v>2.80832160359</v>
+        <v>2.931257539978049</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0008356625565870001</v>
+        <v>0.0008342391821833684</v>
       </c>
       <c r="G36" t="n">
-        <v>0.00229021663869</v>
+        <v>0.002288394173922251</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2900998414903766</v>
+        <v>0.2814822085856372</v>
       </c>
     </row>
     <row r="37">
@@ -1596,19 +1596,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-0.585569689913</v>
+        <v>-1.062590427243404</v>
       </c>
       <c r="E37" t="n">
-        <v>1.73836579849</v>
+        <v>1.871076141325134</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0387699160667</v>
+        <v>0.03856354337571777</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0672798536529</v>
+        <v>0.06696585371812173</v>
       </c>
       <c r="H37" t="n">
-        <v>0.391243907603922</v>
+        <v>0.3834987072484752</v>
       </c>
     </row>
     <row r="38">
@@ -1628,19 +1628,19 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-0.5205940707309999</v>
+        <v>-0.8394630839806072</v>
       </c>
       <c r="E38" t="n">
-        <v>1.13845817269</v>
+        <v>1.277897202644129</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0479168628355</v>
+        <v>0.04772949401587948</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0100700726435</v>
+        <v>0.01003932053592344</v>
       </c>
       <c r="H38" t="n">
-        <v>0.05404668008770486</v>
+        <v>0.04193678361363862</v>
       </c>
     </row>
     <row r="39">
@@ -1660,19 +1660,19 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-0.31446018237</v>
+        <v>-0.6540620394919872</v>
       </c>
       <c r="E39" t="n">
-        <v>1.09860850452</v>
+        <v>1.232621104379739</v>
       </c>
       <c r="F39" t="n">
-        <v>0.014037098672</v>
+        <v>0.01398164476056463</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0142351218443</v>
+        <v>0.01418837692680197</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1085196073335126</v>
+        <v>0.1031048892892183</v>
       </c>
     </row>
     <row r="40">
@@ -1692,19 +1692,19 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.201593227286</v>
+        <v>-0.3799059222347245</v>
       </c>
       <c r="E40" t="n">
-        <v>1.17745490363</v>
+        <v>1.310903341516889</v>
       </c>
       <c r="F40" t="n">
-        <v>0.00675647051112</v>
+        <v>0.006713918427256124</v>
       </c>
       <c r="G40" t="n">
-        <v>0.00559159742981</v>
+        <v>0.005559856255373023</v>
       </c>
       <c r="H40" t="n">
-        <v>0.63616254979042</v>
+        <v>0.6238562885384713</v>
       </c>
     </row>
     <row r="41">
@@ -1724,19 +1724,19 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-1.16595309732</v>
+        <v>-1.185471209248934</v>
       </c>
       <c r="E41" t="n">
-        <v>0.93016181202</v>
+        <v>1.060883544598568</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0584157817263</v>
+        <v>0.0583691608552116</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0517880452898</v>
+        <v>0.05178508614058397</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.7943708299608332</v>
+        <v>-0.7959260774577648</v>
       </c>
     </row>
     <row r="42">
@@ -1756,19 +1756,19 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-0.350675446435</v>
+        <v>-0.6337750775090023</v>
       </c>
       <c r="E42" t="n">
-        <v>1.02268955487</v>
+        <v>1.156162531264648</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0442571844608</v>
+        <v>0.04410927874233642</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0248614343186</v>
+        <v>0.02479398138514406</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.004798026822050439</v>
+        <v>-0.009251089510564636</v>
       </c>
     </row>
     <row r="43">
@@ -1788,19 +1788,19 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-0.378433879658</v>
+        <v>-0.6766930134720184</v>
       </c>
       <c r="E43" t="n">
-        <v>1.0788295271</v>
+        <v>1.2377607065162</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0570147554677</v>
+        <v>0.05684396186309942</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0649623639516</v>
+        <v>0.06476789448258455</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.002759566551324699</v>
+        <v>-0.003412010433812007</v>
       </c>
     </row>
     <row r="44">
@@ -1820,19 +1820,19 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-0.395917423398</v>
+        <v>-0.8311354663916193</v>
       </c>
       <c r="E44" t="n">
-        <v>1.35952991137</v>
+        <v>1.47341906875742</v>
       </c>
       <c r="F44" t="n">
-        <v>0.00204591106519</v>
+        <v>0.002035203287275435</v>
       </c>
       <c r="G44" t="n">
-        <v>0.00204538047573</v>
+        <v>0.002036900301318202</v>
       </c>
       <c r="H44" t="n">
-        <v>0.145557807095531</v>
+        <v>0.1310214981875113</v>
       </c>
     </row>
     <row r="45">
@@ -1852,19 +1852,19 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-0.0466255110609</v>
+        <v>-0.4387932972999553</v>
       </c>
       <c r="E45" t="n">
-        <v>1.40280594672</v>
+        <v>1.567079211169831</v>
       </c>
       <c r="F45" t="n">
-        <v>0.00555224360262</v>
+        <v>0.005530954450153263</v>
       </c>
       <c r="G45" t="n">
-        <v>0.00237393185547</v>
+        <v>0.002364562155903739</v>
       </c>
       <c r="H45" t="n">
-        <v>0.4557540016372208</v>
+        <v>0.4529016994302859</v>
       </c>
     </row>
     <row r="46">
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.206435859533</v>
+        <v>-0.6349721939816533</v>
       </c>
       <c r="E46" t="n">
-        <v>1.2552322528</v>
+        <v>1.442517882844774</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.589583379570624</v>
+        <v>0.6099463589373633</v>
       </c>
     </row>
     <row r="47">
@@ -1916,19 +1916,19 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-0.406261685851</v>
+        <v>-0.5489939649377273</v>
       </c>
       <c r="E47" t="n">
-        <v>1.10296131815</v>
+        <v>1.229371295358139</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0467499394096</v>
+        <v>0.04665030809645965</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0213215710028</v>
+        <v>0.02129466742348883</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.0528447136256438</v>
+        <v>-0.05812985456384867</v>
       </c>
     </row>
     <row r="48">
@@ -1948,19 +1948,19 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-1.14231655962</v>
+        <v>-1.116657114078312</v>
       </c>
       <c r="E48" t="n">
-        <v>1.32578176427</v>
+        <v>1.454807323940699</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0307354761873</v>
+        <v>0.03072363793507914</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0427420628158</v>
+        <v>0.04275933703978188</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.6705114435093917</v>
+        <v>-0.6718145382711538</v>
       </c>
     </row>
     <row r="49">
@@ -1980,19 +1980,19 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-1.15667183989</v>
+        <v>-1.094540882477102</v>
       </c>
       <c r="E49" t="n">
-        <v>0.744349969553</v>
+        <v>0.8171454185880833</v>
       </c>
       <c r="F49" t="n">
-        <v>0.00165575969022</v>
+        <v>0.001653923814193232</v>
       </c>
       <c r="G49" t="n">
-        <v>0.00142455778052</v>
+        <v>0.001426063804658475</v>
       </c>
       <c r="H49" t="n">
-        <v>-1.18970576681422</v>
+        <v>-1.18660019541299</v>
       </c>
     </row>
     <row r="50">
@@ -2012,19 +2012,19 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-0.618851602768</v>
+        <v>-0.6921576662762163</v>
       </c>
       <c r="E50" t="n">
-        <v>1.17614552843</v>
+        <v>1.304716575284282</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0253249070886</v>
+        <v>0.02528961876032183</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0101114217383</v>
+        <v>0.0101056016224966</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.01582102192198009</v>
+        <v>-0.01862483644535784</v>
       </c>
     </row>
     <row r="51">
@@ -2044,19 +2044,19 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-0.431983151973</v>
+        <v>-0.445892681710669</v>
       </c>
       <c r="E51" t="n">
-        <v>1.26741176491</v>
+        <v>1.404075611496136</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0158171642048</v>
+        <v>0.0158066661610113</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0128908363899</v>
+        <v>0.01289051848792633</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.163485756936399</v>
+        <v>-0.1649493526320933</v>
       </c>
     </row>
     <row r="52">
@@ -2076,19 +2076,19 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-1.18648456916</v>
+        <v>-1.255929981056236</v>
       </c>
       <c r="E52" t="n">
-        <v>1.38816392469</v>
+        <v>1.547858268487845</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0614343187816</v>
+        <v>0.06139146274020566</v>
       </c>
       <c r="G52" t="n">
-        <v>0.008136275444169999</v>
+        <v>0.008130546806228869</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1464805264660307</v>
+        <v>-0.149569812054573</v>
       </c>
     </row>
     <row r="53">
@@ -2108,19 +2108,19 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-0.18446435028</v>
+        <v>-0.1907084223121025</v>
       </c>
       <c r="E53" t="n">
-        <v>0.241857255212</v>
+        <v>0.2708915917610355</v>
       </c>
       <c r="F53" t="n">
-        <v>0.00414937876429</v>
+        <v>0.004138824405410624</v>
       </c>
       <c r="G53" t="n">
-        <v>0.00253313206028</v>
+        <v>0.00253460865202631</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.03327455192314588</v>
+        <v>-0.034087605624189</v>
       </c>
     </row>
     <row r="54">
@@ -2140,19 +2140,19 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-1.4346110164</v>
+        <v>-1.566923586373836</v>
       </c>
       <c r="E54" t="n">
-        <v>2.60022894298</v>
+        <v>2.744499528299671</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0106520955334</v>
+        <v>0.01063430112339377</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0120489011997</v>
+        <v>0.01203372607031031</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2094013579226894</v>
+        <v>0.2060442805357887</v>
       </c>
     </row>
     <row r="55">
@@ -2172,19 +2172,19 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-0.710944163148</v>
+        <v>-0.8270061882888369</v>
       </c>
       <c r="E55" t="n">
-        <v>1.21889635295</v>
+        <v>1.31458265919151</v>
       </c>
       <c r="F55" t="n">
-        <v>0.00736783217861</v>
+        <v>0.007350265468685529</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0134333250369</v>
+        <v>0.01342177851196353</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.07486209360487717</v>
+        <v>-0.07959677021177614</v>
       </c>
     </row>
     <row r="56">
@@ -2204,19 +2204,19 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.037921904242</v>
+        <v>-0.04173177417866603</v>
       </c>
       <c r="E56" t="n">
-        <v>1.59932823853</v>
+        <v>1.67690592480747</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0371270666981</v>
+        <v>0.037039175855821</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0204955761656</v>
+        <v>0.02048761541679048</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2670410442567883</v>
+        <v>0.2616822264962293</v>
       </c>
     </row>
     <row r="57">
@@ -2236,19 +2236,19 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-0.0609629836121</v>
+        <v>-0.2451945523061605</v>
       </c>
       <c r="E57" t="n">
-        <v>0.706539928752</v>
+        <v>0.7696251965576106</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0025481929961</v>
+        <v>0.002538912985052564</v>
       </c>
       <c r="G57" t="n">
-        <v>0.00447930021362</v>
+        <v>0.004473153245836787</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.05436192305484644</v>
+        <v>-0.06350147963605224</v>
       </c>
     </row>
     <row r="58">
@@ -2268,19 +2268,19 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.0722905686849</v>
+        <v>-0.07312779113415324</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7940891150129999</v>
+        <v>0.8721532041424895</v>
       </c>
       <c r="F58" t="n">
-        <v>0.000851099504103</v>
+        <v>0.000848572266662836</v>
       </c>
       <c r="G58" t="n">
-        <v>0.00768605870248</v>
+        <v>0.007677931736909041</v>
       </c>
       <c r="H58" t="n">
-        <v>0.08801166606855482</v>
+        <v>0.08139667547073515</v>
       </c>
     </row>
     <row r="59">
@@ -2300,19 +2300,19 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>-0.48311229221</v>
+        <v>-0.8200715991894203</v>
       </c>
       <c r="E59" t="n">
-        <v>1.62445295008</v>
+        <v>1.729528957652171</v>
       </c>
       <c r="F59" t="n">
-        <v>0.000121422533491</v>
+        <v>0.0001208874148053784</v>
       </c>
       <c r="G59" t="n">
-        <v>0.000116441197947</v>
+        <v>0.000116078180018505</v>
       </c>
       <c r="H59" t="n">
-        <v>0.07912497529873885</v>
+        <v>0.06438680790805673</v>
       </c>
     </row>
     <row r="60">
@@ -2332,19 +2332,19 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-0.152144794094</v>
+        <v>-0.811517541464768</v>
       </c>
       <c r="E60" t="n">
-        <v>1.34173354498</v>
+        <v>1.515250501627441</v>
       </c>
       <c r="F60" t="n">
-        <v>0.00127881984373</v>
+        <v>0.001270711355650555</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0006628728840510001</v>
+        <v>0.0006584496181030704</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2898328157377561</v>
+        <v>0.3005781336320679</v>
       </c>
     </row>
     <row r="61">
@@ -2364,19 +2364,19 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-0.206624247312</v>
+        <v>-0.6716061378924554</v>
       </c>
       <c r="E61" t="n">
-        <v>1.20774673245</v>
+        <v>1.308902355245212</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0009920322267070001</v>
+        <v>0.0009863264663523257</v>
       </c>
       <c r="G61" t="n">
-        <v>0.000403916618104</v>
+        <v>0.0004021502918672821</v>
       </c>
       <c r="H61" t="n">
-        <v>0.104921472901065</v>
+        <v>0.08915329243806003</v>
       </c>
     </row>
     <row r="62">
@@ -2396,19 +2396,19 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.171048723174</v>
+        <v>-0.2744081064783854</v>
       </c>
       <c r="E62" t="n">
-        <v>0.993808815817</v>
+        <v>1.054222229380963</v>
       </c>
       <c r="F62" t="n">
-        <v>3.73711617625e-06</v>
+        <v>3.713619660780529e-06</v>
       </c>
       <c r="G62" t="n">
-        <v>1.4417227178e-06</v>
+        <v>1.436010480470024e-06</v>
       </c>
       <c r="H62" t="n">
-        <v>0.3381444740900852</v>
+        <v>0.312075025858638</v>
       </c>
     </row>
     <row r="63">
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.021939823949</v>
+        <v>-0.6267206945155257</v>
       </c>
       <c r="E63" t="n">
-        <v>1.15000934848</v>
+        <v>1.285886353816146</v>
       </c>
       <c r="F63" t="n">
-        <v>0.00035983858872</v>
+        <v>0.0003573475405796132</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0009890801055420001</v>
+        <v>0.0009827772789274423</v>
       </c>
       <c r="H63" t="n">
-        <v>0.4902951366331454</v>
+        <v>0.4793724230818031</v>
       </c>
     </row>
     <row r="64">
@@ -2460,19 +2460,19 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.115133634566</v>
+        <v>-0.5953726223447253</v>
       </c>
       <c r="E64" t="n">
-        <v>1.22936444518</v>
+        <v>1.36555376513563</v>
       </c>
       <c r="F64" t="n">
-        <v>0.000370553993771</v>
+        <v>0.0003677644666070825</v>
       </c>
       <c r="G64" t="n">
-        <v>0.000747311452801</v>
+        <v>0.0007420919383363981</v>
       </c>
       <c r="H64" t="n">
-        <v>0.5617570356728718</v>
+        <v>0.5535608569474437</v>
       </c>
     </row>
     <row r="65">
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.867334925567</v>
+        <v>-0.4122377622670204</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2121566507867767</v>
+        <v>0.133305024752195</v>
       </c>
     </row>
     <row r="66">
@@ -2524,19 +2524,19 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>7.03913015102</v>
+        <v>8.057349517993263</v>
       </c>
       <c r="E66" t="n">
-        <v>4.04545046853</v>
+        <v>4.225862839170569</v>
       </c>
       <c r="F66" t="n">
-        <v>0.201789652742</v>
+        <v>0.2038259757486596</v>
       </c>
       <c r="G66" t="n">
-        <v>0.202790179213</v>
+        <v>0.2046807347154472</v>
       </c>
       <c r="H66" t="n">
-        <v>0.8210045362291973</v>
+        <v>0.8325517876860422</v>
       </c>
     </row>
     <row r="67">
@@ -2556,19 +2556,19 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>-0.352006364023</v>
+        <v>-0.6261888636491686</v>
       </c>
       <c r="E67" t="n">
-        <v>1.40331204653</v>
+        <v>1.58160788097752</v>
       </c>
       <c r="F67" t="n">
-        <v>0.00110441132338</v>
+        <v>0.001101905110036286</v>
       </c>
       <c r="G67" t="n">
-        <v>0.000356989815853</v>
+        <v>0.0003559310384868904</v>
       </c>
       <c r="H67" t="n">
-        <v>0.4733474743995325</v>
+        <v>0.4712476053448489</v>
       </c>
     </row>
     <row r="68">
@@ -2588,19 +2588,19 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>-3.23727603249</v>
+        <v>-3.05761013629503</v>
       </c>
       <c r="E68" t="n">
-        <v>3.43543082024</v>
+        <v>3.617524286203744</v>
       </c>
       <c r="F68" t="n">
-        <v>0.00128640433635</v>
+        <v>0.00128917154610057</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0140088248779</v>
+        <v>0.0140323842393755</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.027510989905156</v>
+        <v>-1.018341692228852</v>
       </c>
     </row>
     <row r="69">
@@ -2620,19 +2620,19 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>6.80503735071</v>
+        <v>7.481088964386373</v>
       </c>
       <c r="E69" t="n">
-        <v>1.29844161487</v>
+        <v>1.451635852202915</v>
       </c>
       <c r="F69" t="n">
-        <v>1.10793638828</v>
+        <v>1.113631491266617</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0816732545424</v>
+        <v>0.08219777203122257</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.5470671130628268</v>
+        <v>-0.5496359392888062</v>
       </c>
     </row>
     <row r="70">
@@ -2652,19 +2652,19 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>3.8675600083</v>
+        <v>5.105929506821671</v>
       </c>
       <c r="E70" t="n">
-        <v>4.73137144764</v>
+        <v>4.890890243299539</v>
       </c>
       <c r="F70" t="n">
-        <v>0.200779432136</v>
+        <v>0.2031428419193058</v>
       </c>
       <c r="G70" t="n">
-        <v>0.420838921439</v>
+        <v>0.4258672087285405</v>
       </c>
       <c r="H70" t="n">
-        <v>1.036407845285892</v>
+        <v>1.044825011255757</v>
       </c>
     </row>
     <row r="71">
@@ -2684,19 +2684,19 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-1.04084416127</v>
+        <v>-1.503210797808263</v>
       </c>
       <c r="E71" t="n">
-        <v>1.65524403252</v>
+        <v>1.776576428251997</v>
       </c>
       <c r="F71" t="n">
-        <v>0.259991430751</v>
+        <v>0.258324629839259</v>
       </c>
       <c r="G71" t="n">
-        <v>0.58696079487</v>
+        <v>0.5843294647116171</v>
       </c>
       <c r="H71" t="n">
-        <v>0.5370848225462632</v>
+        <v>0.5322987266769719</v>
       </c>
     </row>
     <row r="72">
@@ -2716,19 +2716,19 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-1.90180107552</v>
+        <v>-1.955194585110154</v>
       </c>
       <c r="E72" t="n">
-        <v>1.68915184937</v>
+        <v>1.835566412346168</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0278188817389</v>
+        <v>0.02778983935449081</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0374072036906</v>
+        <v>0.03738961903363189</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.7043491508883171</v>
+        <v>-0.7067185688667488</v>
       </c>
     </row>
     <row r="73">
@@ -2748,19 +2748,19 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-1.34541373471</v>
+        <v>-1.502506551956384</v>
       </c>
       <c r="E73" t="n">
-        <v>1.64091941385</v>
+        <v>1.784966582185654</v>
       </c>
       <c r="F73" t="n">
-        <v>0.118824939001</v>
+        <v>0.1185623101745862</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0770553441213</v>
+        <v>0.07694029874775783</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1560498125682486</v>
+        <v>0.1492720407523906</v>
       </c>
     </row>
     <row r="74">
@@ -2780,19 +2780,19 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>-0.749413528817</v>
+        <v>-0.8474350237652306</v>
       </c>
       <c r="E74" t="n">
-        <v>1.56089659093</v>
+        <v>1.701632665005026</v>
       </c>
       <c r="F74" t="n">
-        <v>0.00348652711825</v>
+        <v>0.003481144593969772</v>
       </c>
       <c r="G74" t="n">
-        <v>0.00335245749675</v>
+        <v>0.003349513575493607</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.008765026711876622</v>
+        <v>-0.01195359303245436</v>
       </c>
     </row>
     <row r="75">
@@ -2812,19 +2812,19 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>37.412008595</v>
+        <v>39.41850735966046</v>
       </c>
       <c r="E75" t="n">
-        <v>21.5124756902</v>
+        <v>21.6933608040099</v>
       </c>
       <c r="F75" t="n">
-        <v>0.481993329515</v>
+        <v>0.4888572774231453</v>
       </c>
       <c r="G75" t="n">
-        <v>0.383339176097</v>
+        <v>0.3889601950197528</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.1584154498389556</v>
+        <v>-0.1518072946412041</v>
       </c>
     </row>
     <row r="76">
@@ -2844,19 +2844,19 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>-6.31954867191</v>
+        <v>-6.234258155904094</v>
       </c>
       <c r="E76" t="n">
-        <v>2.10944251509</v>
+        <v>2.2637567398895</v>
       </c>
       <c r="F76" t="n">
-        <v>0.793290443355</v>
+        <v>0.7936283177168294</v>
       </c>
       <c r="G76" t="n">
-        <v>0.274173629319</v>
+        <v>0.2744384942722389</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.2299819583014284</v>
+        <v>-0.2354073473678664</v>
       </c>
     </row>
     <row r="77">
@@ -2876,19 +2876,19 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>-0.762001822263</v>
+        <v>-0.9364230700051435</v>
       </c>
       <c r="E77" t="n">
-        <v>1.29113172721</v>
+        <v>1.435549699805261</v>
       </c>
       <c r="F77" t="n">
-        <v>0.123824821243</v>
+        <v>0.123499982292232</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0289359564993</v>
+        <v>0.02888883816553112</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1697180941441223</v>
+        <v>0.1610945901606708</v>
       </c>
     </row>
     <row r="78">
@@ -2908,19 +2908,19 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>-2.49848207331</v>
+        <v>-2.551594974004834</v>
       </c>
       <c r="E78" t="n">
-        <v>1.88554612001</v>
+        <v>2.023257268230005</v>
       </c>
       <c r="F78" t="n">
-        <v>0.178726317321</v>
+        <v>0.1784575911852102</v>
       </c>
       <c r="G78" t="n">
-        <v>0.206765097353</v>
+        <v>0.2066784043725411</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.520506271062815</v>
+        <v>-0.5240312902113908</v>
       </c>
     </row>
     <row r="79">
@@ -2940,19 +2940,19 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>-1.80615709358</v>
+        <v>-1.800051501906597</v>
       </c>
       <c r="E79" t="n">
-        <v>2.33249246494</v>
+        <v>2.474083827419871</v>
       </c>
       <c r="F79" t="n">
-        <v>0.142464907494</v>
+        <v>0.1423808682485835</v>
       </c>
       <c r="G79" t="n">
-        <v>0.141537877756</v>
+        <v>0.1415623649709681</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.7134475170981203</v>
+        <v>-0.714997619448321</v>
       </c>
     </row>
     <row r="80">
@@ -2972,19 +2972,19 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>-4.05290742321</v>
+        <v>-4.074960767974733</v>
       </c>
       <c r="E80" t="n">
-        <v>1.38372142555</v>
+        <v>1.535454194302233</v>
       </c>
       <c r="F80" t="n">
-        <v>1.36665424935</v>
+        <v>1.365555609923484</v>
       </c>
       <c r="G80" t="n">
-        <v>0.492491262838</v>
+        <v>0.4924101422883022</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.078806284597489</v>
+        <v>-1.083480415378868</v>
       </c>
     </row>
     <row r="81">
@@ -3004,19 +3004,19 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>-2.33886282323</v>
+        <v>-2.378491506042879</v>
       </c>
       <c r="E81" t="n">
-        <v>1.40892399841</v>
+        <v>1.54715623950461</v>
       </c>
       <c r="F81" t="n">
-        <v>0.210884630092</v>
+        <v>0.2105914820167392</v>
       </c>
       <c r="G81" t="n">
-        <v>0.274085160659</v>
+        <v>0.2740058187048653</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.9947859015298932</v>
+        <v>-0.9975717031773468</v>
       </c>
     </row>
     <row r="82">
@@ -3036,19 +3036,19 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>-2.09823301768</v>
+        <v>-2.234671264411825</v>
       </c>
       <c r="E82" t="n">
-        <v>1.12136188229</v>
+        <v>1.269678237265892</v>
       </c>
       <c r="F82" t="n">
-        <v>0.420758776066</v>
+        <v>0.4196136166056142</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0704819687231</v>
+        <v>0.07039314788493255</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.8370018091823139</v>
+        <v>-0.8470842261558587</v>
       </c>
     </row>
     <row r="83">
@@ -3068,19 +3068,19 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>-2.71283956589</v>
+        <v>-2.876849245765078</v>
       </c>
       <c r="E83" t="n">
-        <v>1.42608660878</v>
+        <v>1.565564019385768</v>
       </c>
       <c r="F83" t="n">
-        <v>0.392892707456</v>
+        <v>0.3916397748730671</v>
       </c>
       <c r="G83" t="n">
-        <v>0.332255981627</v>
+        <v>0.3317368423484753</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.5852591043597144</v>
+        <v>-0.5938818227051224</v>
       </c>
     </row>
     <row r="84">
@@ -3100,19 +3100,19 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>-3.31432082891</v>
+        <v>-3.241327308155639</v>
       </c>
       <c r="E84" t="n">
-        <v>1.32643050193</v>
+        <v>1.466805208179722</v>
       </c>
       <c r="F84" t="n">
-        <v>0.625393665896</v>
+        <v>0.6248404016056083</v>
       </c>
       <c r="G84" t="n">
-        <v>0.32410326467</v>
+        <v>0.3243955490473847</v>
       </c>
       <c r="H84" t="n">
-        <v>-1.349408052304157</v>
+        <v>-1.34944369214216</v>
       </c>
     </row>
     <row r="85">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>-2.87493721552</v>
+        <v>-3.03472423577924</v>
       </c>
       <c r="E85" t="n">
-        <v>1.43333315173</v>
+        <v>1.575752880062065</v>
       </c>
       <c r="F85" t="n">
-        <v>0.869630884214</v>
+        <v>0.8673207696629333</v>
       </c>
       <c r="G85" t="n">
-        <v>0.586106367749</v>
+        <v>0.5852111425418436</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.8197896567728846</v>
+        <v>-0.8277968619463616</v>
       </c>
     </row>
     <row r="86">
@@ -3164,19 +3164,19 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>-2.41797569689</v>
+        <v>-2.402589152159174</v>
       </c>
       <c r="E86" t="n">
-        <v>1.25933311262</v>
+        <v>1.398788423249897</v>
       </c>
       <c r="F86" t="n">
-        <v>0.172122973655</v>
+        <v>0.1719137280291025</v>
       </c>
       <c r="G86" t="n">
-        <v>0.138794220661</v>
+        <v>0.1388332559608415</v>
       </c>
       <c r="H86" t="n">
-        <v>-1.375045887501802</v>
+        <v>-1.376450898709369</v>
       </c>
     </row>
     <row r="87">
@@ -3196,19 +3196,19 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>-0.814877934612</v>
+        <v>-1.282847957868449</v>
       </c>
       <c r="E87" t="n">
-        <v>1.39510448674</v>
+        <v>1.53130516155402</v>
       </c>
       <c r="F87" t="n">
-        <v>0.106986377273</v>
+        <v>0.1063666781261646</v>
       </c>
       <c r="G87" t="n">
-        <v>0.171951451479</v>
+        <v>0.1711609008197297</v>
       </c>
       <c r="H87" t="n">
-        <v>0.1030235724584827</v>
+        <v>0.0953753789885381</v>
       </c>
     </row>
     <row r="88">
@@ -3228,19 +3228,19 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>-2.21867444837</v>
+        <v>-2.055873598162417</v>
       </c>
       <c r="E88" t="n">
-        <v>1.43346196713</v>
+        <v>1.563204727527068</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0347255002674</v>
+        <v>0.03473960646351488</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0520841768515</v>
+        <v>0.05217944574064204</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.8787241625962228</v>
+        <v>-0.8775424939843512</v>
       </c>
     </row>
     <row r="89">
@@ -3260,19 +3260,19 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1.24020684778</v>
+        <v>1.277372473742555</v>
       </c>
       <c r="E89" t="n">
-        <v>2.06766379841</v>
+        <v>2.224560128335429</v>
       </c>
       <c r="F89" t="n">
-        <v>0.012872430166</v>
+        <v>0.01287603374396936</v>
       </c>
       <c r="G89" t="n">
-        <v>0.00759601542526</v>
+        <v>0.007598945583990478</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1293627633979222</v>
+        <v>0.1248458915871886</v>
       </c>
     </row>
     <row r="90">
@@ -3292,19 +3292,19 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.303812762675</v>
+        <v>0.0150744400064351</v>
       </c>
       <c r="E90" t="n">
-        <v>1.55417419709</v>
+        <v>1.673511138923089</v>
       </c>
       <c r="F90" t="n">
-        <v>7.32327485499e-05</v>
+        <v>7.294165499473742e-05</v>
       </c>
       <c r="G90" t="n">
-        <v>5.90813009239e-05</v>
+        <v>5.892512717161349e-05</v>
       </c>
       <c r="H90" t="n">
-        <v>0.5154076172854127</v>
+        <v>0.5038961433656786</v>
       </c>
     </row>
     <row r="91">
@@ -3324,19 +3324,19 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>-3.15904235727</v>
+        <v>-3.185438990645384</v>
       </c>
       <c r="E91" t="n">
-        <v>1.32116066259</v>
+        <v>1.475164585786182</v>
       </c>
       <c r="F91" t="n">
-        <v>0.212369759972</v>
+        <v>0.2122596695237024</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0211002908708</v>
+        <v>0.02109555506167189</v>
       </c>
       <c r="H91" t="n">
-        <v>-0.7440221671771607</v>
+        <v>-0.7490371482751446</v>
       </c>
     </row>
     <row r="92">
@@ -3356,19 +3356,19 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>-2.15827483213</v>
+        <v>-2.154779461433631</v>
       </c>
       <c r="E92" t="n">
-        <v>1.89314182616</v>
+        <v>2.032041518939454</v>
       </c>
       <c r="F92" t="n">
-        <v>0.06699057350400001</v>
+        <v>0.06696647843571314</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0402247948407</v>
+        <v>0.04023120757611233</v>
       </c>
       <c r="H92" t="n">
-        <v>-1.290463802867658</v>
+        <v>-1.289895860614676</v>
       </c>
     </row>
     <row r="93">
@@ -3388,19 +3388,19 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>-0.477303677835</v>
+        <v>-0.7239046922175252</v>
       </c>
       <c r="E93" t="n">
-        <v>1.51305919061</v>
+        <v>1.666201075976481</v>
       </c>
       <c r="F93" t="n">
-        <v>0.00607956639241</v>
+        <v>0.006063789351003756</v>
       </c>
       <c r="G93" t="n">
-        <v>0.122034888008</v>
+        <v>0.1217356867900471</v>
       </c>
       <c r="H93" t="n">
-        <v>0.09594124671694626</v>
+        <v>0.09697219909270416</v>
       </c>
     </row>
     <row r="94">
@@ -3420,19 +3420,19 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>-0.744736464972</v>
+        <v>-0.831420742371769</v>
       </c>
       <c r="E94" t="n">
-        <v>2.06604870286</v>
+        <v>2.200007416421723</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0704212547733</v>
+        <v>0.07032292120794348</v>
       </c>
       <c r="G94" t="n">
-        <v>0.458857385411</v>
+        <v>0.4585065522362111</v>
       </c>
       <c r="H94" t="n">
-        <v>0.06953550101187478</v>
+        <v>0.06808553754669155</v>
       </c>
     </row>
     <row r="95">
@@ -3452,19 +3452,19 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>-0.297094599728</v>
+        <v>-0.527880910075329</v>
       </c>
       <c r="E95" t="n">
-        <v>1.41093382049</v>
+        <v>1.539389661281021</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0121327847645</v>
+        <v>0.01209742327943866</v>
       </c>
       <c r="G95" t="n">
-        <v>0.379607164186</v>
+        <v>0.3787761089779318</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1031466973838269</v>
+        <v>0.1002784504428922</v>
       </c>
     </row>
     <row r="96">
@@ -3484,19 +3484,19 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>-1.67769851541</v>
+        <v>-1.489760973636312</v>
       </c>
       <c r="E96" t="n">
-        <v>3.70747989056</v>
+        <v>3.875448554948058</v>
       </c>
       <c r="F96" t="n">
-        <v>0.032593594665</v>
+        <v>0.03265928665514165</v>
       </c>
       <c r="G96" t="n">
-        <v>0.467637201446</v>
+        <v>0.4685210085032726</v>
       </c>
       <c r="H96" t="n">
-        <v>0.1187402717006014</v>
+        <v>0.1245846146215479</v>
       </c>
     </row>
     <row r="97">
@@ -3516,19 +3516,19 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>-2.50896812089</v>
+        <v>-2.209112089935383</v>
       </c>
       <c r="E97" t="n">
-        <v>5.14816603467</v>
+        <v>5.303568280944315</v>
       </c>
       <c r="F97" t="n">
-        <v>0.00593888272572</v>
+        <v>0.005955908053938514</v>
       </c>
       <c r="G97" t="n">
-        <v>0.156051875827</v>
+        <v>0.1565349066832911</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.1815429247179479</v>
+        <v>-0.1716581480060264</v>
       </c>
     </row>
     <row r="98">
@@ -3548,19 +3548,19 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>-4.49241597222</v>
+        <v>-3.492741662027932</v>
       </c>
       <c r="E98" t="n">
-        <v>5.64195983931</v>
+        <v>5.772951894092793</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0180967135441</v>
+        <v>0.01827353074294476</v>
       </c>
       <c r="G98" t="n">
-        <v>0.175038992093</v>
+        <v>0.1768933513851738</v>
       </c>
       <c r="H98" t="n">
-        <v>0.1880742382866618</v>
+        <v>0.1879187837036111</v>
       </c>
     </row>
     <row r="99">
@@ -3580,19 +3580,19 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>-1.94310912877</v>
+        <v>-1.719440741532063</v>
       </c>
       <c r="E99" t="n">
-        <v>2.50116292225</v>
+        <v>2.645267502007842</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0821759085795</v>
+        <v>0.08233430999991524</v>
       </c>
       <c r="G99" t="n">
-        <v>0.125558158134</v>
+        <v>0.1258542619877042</v>
       </c>
       <c r="H99" t="n">
-        <v>-0.03144243322914519</v>
+        <v>-0.03129147103617669</v>
       </c>
     </row>
     <row r="100">
@@ -3612,19 +3612,19 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>-0.962852658651</v>
+        <v>-1.05950998822153</v>
       </c>
       <c r="E100" t="n">
-        <v>2.79863885054</v>
+        <v>2.921119333822042</v>
       </c>
       <c r="F100" t="n">
-        <v>0.000835701328551</v>
+        <v>0.0008342842499242688</v>
       </c>
       <c r="G100" t="n">
-        <v>0.00229022552809</v>
+        <v>0.002288417067260812</v>
       </c>
       <c r="H100" t="n">
-        <v>0.2913656563875877</v>
+        <v>0.2833928846580402</v>
       </c>
     </row>
     <row r="101">
@@ -3644,19 +3644,19 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>-0.53004724799</v>
+        <v>-1.006776565672118</v>
       </c>
       <c r="E101" t="n">
-        <v>1.72783176461</v>
+        <v>1.860050291958792</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0387921995032</v>
+        <v>0.03858594402747188</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0673171554769</v>
+        <v>0.06700335103898029</v>
       </c>
       <c r="H101" t="n">
-        <v>0.4473118948372878</v>
+        <v>0.4401283554784197</v>
       </c>
     </row>
     <row r="102">
@@ -3676,19 +3676,19 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>-0.517785476778</v>
+        <v>-0.8362929421570242</v>
       </c>
       <c r="E102" t="n">
-        <v>1.12792805172</v>
+        <v>1.266877147011081</v>
       </c>
       <c r="F102" t="n">
-        <v>0.0479195595503</v>
+        <v>0.04773240034967591</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0100702962498</v>
+        <v>0.01003957909129514</v>
       </c>
       <c r="H102" t="n">
-        <v>0.05687149782616086</v>
+        <v>0.04513510360839579</v>
       </c>
     </row>
     <row r="103">
@@ -3708,19 +3708,19 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>-0.320622390609</v>
+        <v>-0.659814462890107</v>
       </c>
       <c r="E103" t="n">
-        <v>1.08801623629</v>
+        <v>1.221529890221729</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0140364491118</v>
+        <v>0.01398105697116805</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0142341918699</v>
+        <v>0.01418750450634777</v>
       </c>
       <c r="H103" t="n">
-        <v>0.1023312519767838</v>
+        <v>0.09730862368830806</v>
       </c>
     </row>
     <row r="104">
@@ -3740,19 +3740,19 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.162948508633</v>
+        <v>-0.4175055027541341</v>
       </c>
       <c r="E104" t="n">
-        <v>1.16696228595</v>
+        <v>1.299917174685383</v>
       </c>
       <c r="F104" t="n">
-        <v>0.00675397210696</v>
+        <v>0.006711493719601512</v>
       </c>
       <c r="G104" t="n">
-        <v>0.00558941816882</v>
+        <v>0.005557734619170979</v>
       </c>
       <c r="H104" t="n">
-        <v>0.5973502309160938</v>
+        <v>0.5858778583661239</v>
       </c>
     </row>
     <row r="105">
@@ -3772,19 +3772,19 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>-1.16224364256</v>
+        <v>-1.181606924191703</v>
       </c>
       <c r="E105" t="n">
-        <v>0.919849759933</v>
+        <v>1.050085613768115</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0584191936315</v>
+        <v>0.05837269475065233</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0517897364788</v>
+        <v>0.05178685196902458</v>
       </c>
       <c r="H105" t="n">
-        <v>-0.7906474289176013</v>
+        <v>-0.7920465586747749</v>
       </c>
     </row>
     <row r="106">
@@ -3804,19 +3804,19 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>-0.312545717499</v>
+        <v>-0.5957653352719694</v>
       </c>
       <c r="E106" t="n">
-        <v>1.01217114812</v>
+        <v>1.145152881630973</v>
       </c>
       <c r="F106" t="n">
-        <v>0.044274799403</v>
+        <v>0.04412684872961095</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0248708498035</v>
+        <v>0.02480336567931142</v>
       </c>
       <c r="H106" t="n">
-        <v>0.03346404834221328</v>
+        <v>0.02899754673519883</v>
       </c>
     </row>
     <row r="107">
@@ -3836,19 +3836,19 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>-0.363016237361</v>
+        <v>-0.6613742131446498</v>
       </c>
       <c r="E107" t="n">
-        <v>1.06621627425</v>
+        <v>1.224553699996367</v>
       </c>
       <c r="F107" t="n">
-        <v>0.057021838508</v>
+        <v>0.05685089541658048</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0649728303667</v>
+        <v>0.06477831847510572</v>
       </c>
       <c r="H107" t="n">
-        <v>0.01271621588947447</v>
+        <v>0.01201063115259249</v>
       </c>
     </row>
     <row r="108">
@@ -3868,19 +3868,19 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>-0.322502457065</v>
+        <v>-0.7574294358735356</v>
       </c>
       <c r="E108" t="n">
-        <v>1.35059956947</v>
+        <v>1.464071946947287</v>
       </c>
       <c r="F108" t="n">
-        <v>0.00204751294952</v>
+        <v>0.00203681299869909</v>
       </c>
       <c r="G108" t="n">
-        <v>0.00204686379863</v>
+        <v>0.002038389096800066</v>
       </c>
       <c r="H108" t="n">
-        <v>0.2193718774088804</v>
+        <v>0.2054426399547671</v>
       </c>
     </row>
     <row r="109">
@@ -3900,19 +3900,19 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>-0.0743659630929</v>
+        <v>-0.4662032395445714</v>
       </c>
       <c r="E109" t="n">
-        <v>1.38987504934</v>
+        <v>1.553539379455637</v>
       </c>
       <c r="F109" t="n">
-        <v>0.00555053606324</v>
+        <v>0.005529256752829703</v>
       </c>
       <c r="G109" t="n">
-        <v>0.00237329170615</v>
+        <v>0.00236393080997499</v>
       </c>
       <c r="H109" t="n">
-        <v>0.4278741222487614</v>
+        <v>0.4252462669071644</v>
       </c>
     </row>
     <row r="110">
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.251637103212</v>
+        <v>-0.5914315633701039</v>
       </c>
       <c r="E110" t="n">
-        <v>1.24040341593</v>
+        <v>1.426985779052692</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>0.6349574539093572</v>
+        <v>0.6540324987693191</v>
       </c>
     </row>
     <row r="111">
@@ -3964,19 +3964,19 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>-0.402224615925</v>
+        <v>-0.5446706502498899</v>
       </c>
       <c r="E111" t="n">
-        <v>1.09305174103</v>
+        <v>1.219000243259716</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0467532337704</v>
+        <v>0.04665378291204608</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0213222786854</v>
+        <v>0.02129543109416161</v>
       </c>
       <c r="H111" t="n">
-        <v>-0.04879331780873741</v>
+        <v>-0.05378520112738761</v>
       </c>
     </row>
     <row r="112">
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>-1.14176629597</v>
+        <v>-1.115966475212715</v>
       </c>
       <c r="E112" t="n">
-        <v>1.31561276345</v>
+        <v>1.444162923436365</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0307364055286</v>
+        <v>0.03072463545527404</v>
       </c>
       <c r="G112" t="n">
-        <v>0.042742064332</v>
+        <v>0.04275939142459991</v>
       </c>
       <c r="H112" t="n">
-        <v>-0.6699585536881547</v>
+        <v>-0.6711207924558593</v>
       </c>
     </row>
     <row r="113">
@@ -4028,19 +4028,19 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>-1.1613296599</v>
+        <v>-1.099318901477409</v>
       </c>
       <c r="E113" t="n">
-        <v>0.738677782225</v>
+        <v>0.8112106924234697</v>
       </c>
       <c r="F113" t="n">
-        <v>0.00165586968717</v>
+        <v>0.001654039748924187</v>
       </c>
       <c r="G113" t="n">
-        <v>0.00142445078692</v>
+        <v>0.001425953306545777</v>
       </c>
       <c r="H113" t="n">
-        <v>-1.194362030157836</v>
+        <v>-1.191373767124437</v>
       </c>
     </row>
     <row r="114">
@@ -4060,19 +4060,19 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>-0.615036382784</v>
+        <v>-0.6881475304052365</v>
       </c>
       <c r="E114" t="n">
-        <v>1.16611150563</v>
+        <v>1.294214126266757</v>
       </c>
       <c r="F114" t="n">
-        <v>0.025326575301</v>
+        <v>0.02529135904236795</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0101117412841</v>
+        <v>0.01010593873526431</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.01198265172930313</v>
+        <v>-0.0145875027408704</v>
       </c>
     </row>
     <row r="115">
@@ -4092,19 +4092,19 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>-0.417257307582</v>
+        <v>-0.4311520101823785</v>
       </c>
       <c r="E115" t="n">
-        <v>1.25666216879</v>
+        <v>1.392823160212742</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0158197137715</v>
+        <v>0.01580922115009789</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0128927053041</v>
+        <v>0.0128923887512405</v>
       </c>
       <c r="H115" t="n">
-        <v>-0.1487202024960776</v>
+        <v>-0.1501670826861812</v>
       </c>
     </row>
     <row r="116">
@@ -4124,19 +4124,19 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>-1.16404799968</v>
+        <v>-1.233412587033089</v>
       </c>
       <c r="E116" t="n">
-        <v>1.37583818128</v>
+        <v>1.534955179253039</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0614467132988</v>
+        <v>0.06140381969799671</v>
       </c>
       <c r="G116" t="n">
-        <v>0.00813817406686</v>
+        <v>0.008132454975524473</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.1238078139557786</v>
+        <v>-0.1268001259408513</v>
       </c>
     </row>
     <row r="117">
@@ -4156,19 +4156,19 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>-0.182614520929</v>
+        <v>-0.1888022237731324</v>
       </c>
       <c r="E117" t="n">
-        <v>0.23956800555</v>
+        <v>0.2684982688260451</v>
       </c>
       <c r="F117" t="n">
-        <v>0.00415017105943</v>
+        <v>0.004139648334165229</v>
       </c>
       <c r="G117" t="n">
-        <v>0.00253306557207</v>
+        <v>0.002534538583482617</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.03142192065033189</v>
+        <v>-0.03217841587701553</v>
       </c>
     </row>
     <row r="118">
@@ -4188,19 +4188,19 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>-1.3684203195</v>
+        <v>-1.500582258272809</v>
       </c>
       <c r="E118" t="n">
-        <v>2.58879421079</v>
+        <v>2.732527932189832</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0106592564061</v>
+        <v>0.0106414731086815</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0120569903715</v>
+        <v>0.01204183513183906</v>
       </c>
       <c r="H118" t="n">
-        <v>0.2766960764867932</v>
+        <v>0.2735805427713345</v>
       </c>
     </row>
     <row r="119">
@@ -4220,19 +4220,19 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>-0.702761319124</v>
+        <v>-0.8185549147474935</v>
       </c>
       <c r="E119" t="n">
-        <v>1.21134336639</v>
+        <v>1.306679415855561</v>
       </c>
       <c r="F119" t="n">
-        <v>0.00736897159609</v>
+        <v>0.007351444887975846</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0134341853098</v>
+        <v>0.01342266540494832</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.06662682728399982</v>
+        <v>-0.07108180431633082</v>
       </c>
     </row>
     <row r="120">
@@ -4252,19 +4252,19 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.0376526517905</v>
+        <v>-0.04166278175095073</v>
       </c>
       <c r="E120" t="n">
-        <v>1.59324061882</v>
+        <v>1.67053602685503</v>
       </c>
       <c r="F120" t="n">
-        <v>0.0371307166101</v>
+        <v>0.03704310133027457</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0204949842107</v>
+        <v>0.02048707018827469</v>
       </c>
       <c r="H120" t="n">
-        <v>0.2667711751302093</v>
+        <v>0.2617514283440148</v>
       </c>
     </row>
     <row r="121">
@@ -4284,19 +4284,19 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>-0.0426413845391</v>
+        <v>-0.2264918385862735</v>
       </c>
       <c r="E121" t="n">
-        <v>0.701555589288</v>
+        <v>0.7644114755372078</v>
       </c>
       <c r="F121" t="n">
-        <v>0.00254896307069</v>
+        <v>0.002539703846968917</v>
       </c>
       <c r="G121" t="n">
-        <v>0.00447998206231</v>
+        <v>0.004473846756741962</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.03603911382424885</v>
+        <v>-0.04476470085525985</v>
       </c>
     </row>
     <row r="122">
@@ -4316,19 +4316,19 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.07830091075579999</v>
+        <v>-0.0667786882101451</v>
       </c>
       <c r="E122" t="n">
-        <v>0.787941375312</v>
+        <v>0.8657203222444787</v>
       </c>
       <c r="F122" t="n">
-        <v>0.000851233032474</v>
+        <v>0.0008487118362489161</v>
       </c>
       <c r="G122" t="n">
-        <v>0.00768632626457</v>
+        <v>0.007678217492229913</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0940229523486158</v>
+        <v>0.0877555964919452</v>
       </c>
     </row>
     <row r="123">
@@ -4348,19 +4348,19 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>-0.425831418901</v>
+        <v>-0.7621988782958056</v>
       </c>
       <c r="E123" t="n">
-        <v>1.6161594104</v>
+        <v>1.720849771005994</v>
       </c>
       <c r="F123" t="n">
-        <v>0.000121499409645</v>
+        <v>0.0001209651930658131</v>
       </c>
       <c r="G123" t="n">
-        <v>0.000116506460775</v>
+        <v>0.0001161440876766285</v>
       </c>
       <c r="H123" t="n">
-        <v>0.136729466462282</v>
+        <v>0.1227756212748288</v>
       </c>
     </row>
     <row r="124">
@@ -4380,19 +4380,19 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>-0.102754556919</v>
+        <v>-0.7632043408544398</v>
       </c>
       <c r="E124" t="n">
-        <v>1.32799990424</v>
+        <v>1.500867939360617</v>
       </c>
       <c r="F124" t="n">
-        <v>0.00127939456313</v>
+        <v>0.001271269840571746</v>
       </c>
       <c r="G124" t="n">
-        <v>0.000663208652742</v>
+        <v>0.0006587785659540262</v>
       </c>
       <c r="H124" t="n">
-        <v>0.3394416793312205</v>
+        <v>0.3494330191247341</v>
       </c>
     </row>
     <row r="125">
@@ -4412,19 +4412,19 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>-0.118352601703</v>
+        <v>-0.5830550543271307</v>
       </c>
       <c r="E125" t="n">
-        <v>1.19975238057</v>
+        <v>1.300535895503607</v>
       </c>
       <c r="F125" t="n">
-        <v>0.000992972183069</v>
+        <v>0.0009872704139666489</v>
       </c>
       <c r="G125" t="n">
-        <v>0.000404267234877</v>
+        <v>0.0004025019007338972</v>
       </c>
       <c r="H125" t="n">
-        <v>0.1934686944508268</v>
+        <v>0.1783825916602533</v>
       </c>
     </row>
     <row r="126">
@@ -4444,19 +4444,19 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.206276633784</v>
+        <v>-0.2378488580534244</v>
       </c>
       <c r="E126" t="n">
-        <v>0.989064855927</v>
+        <v>1.049257769780287</v>
       </c>
       <c r="F126" t="n">
-        <v>3.73889104458e-06</v>
+        <v>3.715458426444341e-06</v>
       </c>
       <c r="G126" t="n">
-        <v>1.44218298148e-06</v>
+        <v>1.436488348272429e-06</v>
       </c>
       <c r="H126" t="n">
-        <v>0.3734311485270814</v>
+        <v>0.3488492780967967</v>
       </c>
     </row>
     <row r="127">
@@ -4476,19 +4476,19 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.0464411270249</v>
+        <v>-0.6018644817689212</v>
       </c>
       <c r="E127" t="n">
-        <v>1.13933362116</v>
+        <v>1.274711515554916</v>
       </c>
       <c r="F127" t="n">
-        <v>0.000359931064536</v>
+        <v>0.0003574413263331515</v>
       </c>
       <c r="G127" t="n">
-        <v>0.000989319322959</v>
+        <v>0.0009830199807626422</v>
       </c>
       <c r="H127" t="n">
-        <v>0.5149111676925555</v>
+        <v>0.5045053026148993</v>
       </c>
     </row>
     <row r="128">
@@ -4508,19 +4508,19 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.12436573898</v>
+        <v>-0.5856210822992147</v>
       </c>
       <c r="E128" t="n">
-        <v>1.21859589702</v>
+        <v>1.354281329669416</v>
       </c>
       <c r="F128" t="n">
-        <v>0.000370592008835</v>
+        <v>0.0003678044350744251</v>
       </c>
       <c r="G128" t="n">
-        <v>0.000747378343253</v>
+        <v>0.0007421626887941606</v>
       </c>
       <c r="H128" t="n">
-        <v>0.5710303254074622</v>
+        <v>0.5634251067442753</v>
       </c>
     </row>
     <row r="129">
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.908162586581</v>
+        <v>-0.3665745663611664</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
@@ -4552,7 +4552,7 @@
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>0.2527191179545474</v>
+        <v>0.1792183641154077</v>
       </c>
     </row>
     <row r="130">
@@ -4572,19 +4572,19 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>6.88061206704</v>
+        <v>7.895494011669935</v>
       </c>
       <c r="E130" t="n">
-        <v>4.01089193823</v>
+        <v>4.189614264244379</v>
       </c>
       <c r="F130" t="n">
-        <v>0.201446886346</v>
+        <v>0.2034739706694639</v>
       </c>
       <c r="G130" t="n">
-        <v>0.202504351203</v>
+        <v>0.2043895449064656</v>
       </c>
       <c r="H130" t="n">
-        <v>0.6716950973214564</v>
+        <v>0.6815180653499953</v>
       </c>
     </row>
     <row r="131">
@@ -4604,19 +4604,19 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>-0.567801613998</v>
+        <v>-0.8405174415649475</v>
       </c>
       <c r="E131" t="n">
-        <v>1.36906123846</v>
+        <v>1.545680007437622</v>
       </c>
       <c r="F131" t="n">
-        <v>0.00110182708715</v>
+        <v>0.00109932638488429</v>
       </c>
       <c r="G131" t="n">
-        <v>0.00035624440407</v>
+        <v>0.0003551924053317754</v>
       </c>
       <c r="H131" t="n">
-        <v>0.2557648584035954</v>
+        <v>0.2545520859274619</v>
       </c>
     </row>
     <row r="132">
@@ -4636,19 +4636,19 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>-3.22042078418</v>
+        <v>-3.041054091568718</v>
       </c>
       <c r="E132" t="n">
-        <v>3.39973671166</v>
+        <v>3.580074545627143</v>
       </c>
       <c r="F132" t="n">
-        <v>0.00128647893952</v>
+        <v>0.001289234026538169</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0140122331756</v>
+        <v>0.01403580163932551</v>
       </c>
       <c r="H132" t="n">
-        <v>-1.010270819210046</v>
+        <v>-1.001437376538561</v>
       </c>
     </row>
     <row r="133">
@@ -4668,19 +4668,19 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>6.76979482684</v>
+        <v>7.447121105483823</v>
       </c>
       <c r="E133" t="n">
-        <v>1.27121294603</v>
+        <v>1.42310338563123</v>
       </c>
       <c r="F133" t="n">
-        <v>1.10757959484</v>
+        <v>1.113285788257627</v>
       </c>
       <c r="G133" t="n">
-        <v>0.08164625446319999</v>
+        <v>0.08217175883465234</v>
       </c>
       <c r="H133" t="n">
-        <v>-0.5798836585006795</v>
+        <v>-0.5810658025956594</v>
       </c>
     </row>
     <row r="134">
@@ -4700,19 +4700,19 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>3.70768115113</v>
+        <v>4.942897886834352</v>
       </c>
       <c r="E134" t="n">
-        <v>4.70050491359</v>
+        <v>4.858513516405205</v>
       </c>
       <c r="F134" t="n">
-        <v>0.200453318501</v>
+        <v>0.2028093901360981</v>
       </c>
       <c r="G134" t="n">
-        <v>0.420197204231</v>
+        <v>0.4252131604671318</v>
       </c>
       <c r="H134" t="n">
-        <v>0.8808868585834517</v>
+        <v>0.8880926404921219</v>
       </c>
     </row>
     <row r="135">
@@ -4732,19 +4732,19 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>-1.04199022694</v>
+        <v>-1.502239090903723</v>
       </c>
       <c r="E135" t="n">
-        <v>1.63121962641</v>
+        <v>1.751375915753561</v>
       </c>
       <c r="F135" t="n">
-        <v>0.260028343458</v>
+        <v>0.2583681238957231</v>
       </c>
       <c r="G135" t="n">
-        <v>0.586944191951</v>
+        <v>0.5843251558267539</v>
       </c>
       <c r="H135" t="n">
-        <v>0.5359204825667874</v>
+        <v>0.5332905146285594</v>
       </c>
     </row>
     <row r="136">
@@ -4764,19 +4764,19 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>-1.89120702722</v>
+        <v>-1.944362152592782</v>
       </c>
       <c r="E136" t="n">
-        <v>1.66112706113</v>
+        <v>1.806175291925305</v>
       </c>
       <c r="F136" t="n">
-        <v>0.027821188307</v>
+        <v>0.02779213840915981</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0374113827315</v>
+        <v>0.03739390405344632</v>
       </c>
       <c r="H136" t="n">
-        <v>-0.6936257845818083</v>
+        <v>-0.6957481990855108</v>
       </c>
     </row>
     <row r="137">
@@ -4796,19 +4796,19 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>-1.40953663523</v>
+        <v>-1.565652361336978</v>
       </c>
       <c r="E137" t="n">
-        <v>1.61380045513</v>
+        <v>1.756531407714834</v>
       </c>
       <c r="F137" t="n">
-        <v>0.118748857079</v>
+        <v>0.1184873435283136</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0770051401915</v>
+        <v>0.07689086433253514</v>
       </c>
       <c r="H137" t="n">
-        <v>0.09095100001699219</v>
+        <v>0.08506729177339967</v>
       </c>
     </row>
     <row r="138">
@@ -4828,19 +4828,19 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>-0.758432079428</v>
+        <v>-0.8558692023379111</v>
       </c>
       <c r="E138" t="n">
-        <v>1.5340854779</v>
+        <v>1.673517060734375</v>
       </c>
       <c r="F138" t="n">
-        <v>0.00348626554326</v>
+        <v>0.003480902292612643</v>
       </c>
       <c r="G138" t="n">
-        <v>0.00335214242047</v>
+        <v>0.003349218468611246</v>
       </c>
       <c r="H138" t="n">
-        <v>-0.01785087743905178</v>
+        <v>-0.02045883985820618</v>
       </c>
     </row>
     <row r="139">
@@ -4860,19 +4860,19 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>37.4359096066</v>
+        <v>39.44446645920699</v>
       </c>
       <c r="E139" t="n">
-        <v>21.4798538444</v>
+        <v>21.65917135261719</v>
       </c>
       <c r="F139" t="n">
-        <v>0.482078692036</v>
+        <v>0.4889495266142537</v>
       </c>
       <c r="G139" t="n">
-        <v>0.383405647208</v>
+        <v>0.3890324523406554</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.1410493193610307</v>
+        <v>-0.1332160098608259</v>
       </c>
     </row>
     <row r="140">
@@ -4892,19 +4892,19 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>-6.34947814981</v>
+        <v>-6.263791030074106</v>
       </c>
       <c r="E140" t="n">
-        <v>2.08154644066</v>
+        <v>2.234518852677336</v>
       </c>
       <c r="F140" t="n">
-        <v>0.793009750301</v>
+        <v>0.7933485736054485</v>
       </c>
       <c r="G140" t="n">
-        <v>0.274087115617</v>
+        <v>0.2743532374009605</v>
       </c>
       <c r="H140" t="n">
-        <v>-0.2618569600518317</v>
+        <v>-0.2668296462105757</v>
       </c>
     </row>
     <row r="141">
@@ -4924,19 +4924,19 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>-0.774151971394</v>
+        <v>-0.9480254652206477</v>
       </c>
       <c r="E141" t="n">
-        <v>1.26471437578</v>
+        <v>1.407859321144977</v>
       </c>
       <c r="F141" t="n">
-        <v>0.123815984995</v>
+        <v>0.1234919425119635</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0289321932389</v>
+        <v>0.02888523047289625</v>
       </c>
       <c r="H141" t="n">
-        <v>0.1574538704032014</v>
+        <v>0.1493636529114273</v>
       </c>
     </row>
     <row r="142">
@@ -4956,19 +4956,19 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>-2.48566234667</v>
+        <v>-2.538564479354888</v>
       </c>
       <c r="E142" t="n">
-        <v>1.85950053145</v>
+        <v>1.995947279397403</v>
       </c>
       <c r="F142" t="n">
-        <v>0.178760561829</v>
+        <v>0.1784924098590824</v>
       </c>
       <c r="G142" t="n">
-        <v>0.206790657627</v>
+        <v>0.2067043816048845</v>
       </c>
       <c r="H142" t="n">
-        <v>-0.5074264755579927</v>
+        <v>-0.510729676113908</v>
       </c>
     </row>
     <row r="143">
@@ -4988,19 +4988,19 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>-1.80776839028</v>
+        <v>-1.801402079719294</v>
       </c>
       <c r="E143" t="n">
-        <v>2.30571060763</v>
+        <v>2.446001283257204</v>
       </c>
       <c r="F143" t="n">
-        <v>0.142466332018</v>
+        <v>0.1423826723448756</v>
       </c>
       <c r="G143" t="n">
-        <v>0.14153492015</v>
+        <v>0.1415597825037599</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.7150767444471517</v>
+        <v>-0.7163631203818688</v>
       </c>
     </row>
     <row r="144">
@@ -5020,19 +5020,19 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>-4.04113521085</v>
+        <v>-4.062836227065181</v>
       </c>
       <c r="E144" t="n">
-        <v>1.35637035976</v>
+        <v>1.506789198580805</v>
       </c>
       <c r="F144" t="n">
-        <v>1.36681525096</v>
+        <v>1.365719323601801</v>
       </c>
       <c r="G144" t="n">
-        <v>0.492551962025</v>
+        <v>0.4924727444461012</v>
       </c>
       <c r="H144" t="n">
-        <v>-1.066669165399325</v>
+        <v>-1.070977763329561</v>
       </c>
     </row>
     <row r="145">
@@ -5052,19 +5052,19 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>-2.33548180434</v>
+        <v>-2.374851753743057</v>
       </c>
       <c r="E145" t="n">
-        <v>1.38285410254</v>
+        <v>1.519821485875772</v>
       </c>
       <c r="F145" t="n">
-        <v>0.210904209695</v>
+        <v>0.2106118274380596</v>
       </c>
       <c r="G145" t="n">
-        <v>0.274092764905</v>
+        <v>0.2740141153882296</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.9913583508300627</v>
+        <v>-0.9938804642112498</v>
       </c>
     </row>
     <row r="146">
@@ -5084,19 +5084,19 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>-2.06126333948</v>
+        <v>-2.197728098782892</v>
       </c>
       <c r="E146" t="n">
-        <v>1.09489224309</v>
+        <v>1.2419410239358</v>
       </c>
       <c r="F146" t="n">
-        <v>0.420958678846</v>
+        <v>0.4198141744543834</v>
       </c>
       <c r="G146" t="n">
-        <v>0.07050789431520001</v>
+        <v>0.07041904051264958</v>
       </c>
       <c r="H146" t="n">
-        <v>-0.7995558646865075</v>
+        <v>-0.8096167247686137</v>
       </c>
     </row>
     <row r="147">
@@ -5116,19 +5116,19 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>-2.69817915854</v>
+        <v>-2.861783002677931</v>
       </c>
       <c r="E147" t="n">
-        <v>1.40006928536</v>
+        <v>1.538288281966094</v>
       </c>
       <c r="F147" t="n">
-        <v>0.392990825391</v>
+        <v>0.391740213014491</v>
       </c>
       <c r="G147" t="n">
-        <v>0.332303351417</v>
+        <v>0.331785546999968</v>
       </c>
       <c r="H147" t="n">
-        <v>-0.570278087423659</v>
+        <v>-0.5784614339597205</v>
       </c>
     </row>
     <row r="148">
@@ -5148,19 +5148,19 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>-3.32162266017</v>
+        <v>-3.24865075008417</v>
       </c>
       <c r="E148" t="n">
-        <v>1.30065502803</v>
+        <v>1.439788193282809</v>
       </c>
       <c r="F148" t="n">
-        <v>0.625429595605</v>
+        <v>0.6248786849767353</v>
       </c>
       <c r="G148" t="n">
-        <v>0.324074930807</v>
+        <v>0.3243670209680434</v>
       </c>
       <c r="H148" t="n">
-        <v>-1.35685827639398</v>
+        <v>-1.356910326400762</v>
       </c>
     </row>
     <row r="149">
@@ -5180,19 +5180,19 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>-2.8283672245</v>
+        <v>-2.988078730656574</v>
       </c>
       <c r="E149" t="n">
-        <v>1.40695011525</v>
+        <v>1.54809524366164</v>
       </c>
       <c r="F149" t="n">
-        <v>0.870096692499</v>
+        <v>0.8677875067331721</v>
       </c>
       <c r="G149" t="n">
-        <v>0.586383566142</v>
+        <v>0.5854887733784399</v>
       </c>
       <c r="H149" t="n">
-        <v>-0.7722342537427207</v>
+        <v>-0.7800897062347656</v>
       </c>
     </row>
     <row r="150">
@@ -5212,19 +5212,19 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>-2.40868808912</v>
+        <v>-2.393112565660782</v>
       </c>
       <c r="E150" t="n">
-        <v>1.23299668302</v>
+        <v>1.371174260326158</v>
       </c>
       <c r="F150" t="n">
-        <v>0.172150629471</v>
+        <v>0.1719417913639898</v>
       </c>
       <c r="G150" t="n">
-        <v>0.138806613373</v>
+        <v>0.1388459109958218</v>
       </c>
       <c r="H150" t="n">
-        <v>-1.36565901633704</v>
+        <v>-1.366874675470264</v>
       </c>
     </row>
     <row r="151">
@@ -5244,19 +5244,19 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>-0.723771278762</v>
+        <v>-1.191387085758866</v>
       </c>
       <c r="E151" t="n">
-        <v>1.36899485599</v>
+        <v>1.503923934294549</v>
       </c>
       <c r="F151" t="n">
-        <v>0.107090660309</v>
+        <v>0.1064712818309711</v>
       </c>
       <c r="G151" t="n">
-        <v>0.172108313566</v>
+        <v>0.1713183869108772</v>
       </c>
       <c r="H151" t="n">
-        <v>0.1949733682367949</v>
+        <v>0.1881131670721237</v>
       </c>
     </row>
     <row r="152">
@@ -5276,19 +5276,19 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>-2.19031353033</v>
+        <v>-2.026777577985917</v>
       </c>
       <c r="E152" t="n">
-        <v>1.40860432219</v>
+        <v>1.537137790614973</v>
       </c>
       <c r="F152" t="n">
-        <v>0.0347392216445</v>
+        <v>0.03475368953581744</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0520985701051</v>
+        <v>0.05219420990792512</v>
       </c>
       <c r="H152" t="n">
-        <v>-0.8499745995872887</v>
+        <v>-0.8480964298915761</v>
       </c>
     </row>
     <row r="153">
@@ -5308,19 +5308,19 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1.1776351706</v>
+        <v>1.215426994842139</v>
       </c>
       <c r="E153" t="n">
-        <v>2.03832553218</v>
+        <v>2.193801389229022</v>
       </c>
       <c r="F153" t="n">
-        <v>0.012863811391</v>
+        <v>0.01286745447835036</v>
       </c>
       <c r="G153" t="n">
-        <v>0.00759140438558</v>
+        <v>0.007594386600761021</v>
       </c>
       <c r="H153" t="n">
-        <v>0.06747764524037692</v>
+        <v>0.06360534617126934</v>
       </c>
     </row>
     <row r="154">
@@ -5340,19 +5340,19 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0.212562920458</v>
+        <v>-0.07399237356695565</v>
       </c>
       <c r="E154" t="n">
-        <v>1.5315439316</v>
+        <v>1.649790725242406</v>
       </c>
       <c r="F154" t="n">
-        <v>7.31756302688e-05</v>
+        <v>7.288654779863453e-05</v>
       </c>
       <c r="G154" t="n">
-        <v>5.90259083516e-05</v>
+        <v>5.887094598875587e-05</v>
       </c>
       <c r="H154" t="n">
-        <v>0.423965279922256</v>
+        <v>0.4143940174979432</v>
       </c>
     </row>
     <row r="155">
@@ -5372,19 +5372,19 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>-3.14332600122</v>
+        <v>-3.169371253348019</v>
       </c>
       <c r="E155" t="n">
-        <v>1.29311200875</v>
+        <v>1.445766984757602</v>
       </c>
       <c r="F155" t="n">
-        <v>0.212395904908</v>
+        <v>0.212285997754707</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0211038771091</v>
+        <v>0.02109922933457121</v>
       </c>
       <c r="H155" t="n">
-        <v>-0.7279138765769577</v>
+        <v>-0.7325650558441477</v>
       </c>
     </row>
     <row r="156">
@@ -5404,19 +5404,19 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>-2.15655136874</v>
+        <v>-2.152890158182441</v>
       </c>
       <c r="E156" t="n">
-        <v>1.86686164537</v>
+        <v>2.004484687970254</v>
       </c>
       <c r="F156" t="n">
-        <v>0.0669932105954</v>
+        <v>0.06696925069182942</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0402252297636</v>
+        <v>0.04023170647658871</v>
       </c>
       <c r="H156" t="n">
-        <v>-1.288725053151329</v>
+        <v>-1.287989857238636</v>
       </c>
     </row>
     <row r="157">
@@ -5436,19 +5436,19 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>-0.445755446654</v>
+        <v>-0.6926341405727676</v>
       </c>
       <c r="E157" t="n">
-        <v>1.48331896191</v>
+        <v>1.635003722297479</v>
       </c>
       <c r="F157" t="n">
-        <v>0.0060812072692</v>
+        <v>0.006065395119055223</v>
       </c>
       <c r="G157" t="n">
-        <v>0.122074850208</v>
+        <v>0.1217753896555888</v>
       </c>
       <c r="H157" t="n">
-        <v>0.1276711938689834</v>
+        <v>0.1285013152301895</v>
       </c>
     </row>
     <row r="158">
@@ -5468,19 +5468,19 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>-0.760726612888</v>
+        <v>-0.8467096778248862</v>
       </c>
       <c r="E158" t="n">
-        <v>2.03979423563</v>
+        <v>2.172466324082012</v>
       </c>
       <c r="F158" t="n">
-        <v>0.0704116346504</v>
+        <v>0.07031381400441623</v>
       </c>
       <c r="G158" t="n">
-        <v>0.458781126343</v>
+        <v>0.4584335127046765</v>
       </c>
       <c r="H158" t="n">
-        <v>0.05341417285700256</v>
+        <v>0.05265792416195847</v>
       </c>
     </row>
     <row r="159">
@@ -5500,19 +5500,19 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>-0.31421380639</v>
+        <v>-0.5440873751513919</v>
       </c>
       <c r="E159" t="n">
-        <v>1.38566363028</v>
+        <v>1.512879629919794</v>
       </c>
       <c r="F159" t="n">
-        <v>0.0121311859958</v>
+        <v>0.01209594602695868</v>
       </c>
       <c r="G159" t="n">
-        <v>0.379538814631</v>
+        <v>0.3787111641788853</v>
       </c>
       <c r="H159" t="n">
-        <v>0.08595876841677175</v>
+        <v>0.08396964269199447</v>
       </c>
     </row>
     <row r="160">
@@ -5532,19 +5532,19 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>-1.69439313387</v>
+        <v>-1.506743427569912</v>
       </c>
       <c r="E160" t="n">
-        <v>3.67472747048</v>
+        <v>3.841089413392096</v>
       </c>
       <c r="F160" t="n">
-        <v>0.0325849907639</v>
+        <v>0.032650407704055</v>
       </c>
       <c r="G160" t="n">
-        <v>0.467566901871</v>
+        <v>0.4684498716000084</v>
       </c>
       <c r="H160" t="n">
-        <v>0.1017406272222354</v>
+        <v>0.1073238591646097</v>
       </c>
     </row>
     <row r="161">
@@ -5564,19 +5564,19 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>-2.46266124024</v>
+        <v>-2.162128373888617</v>
       </c>
       <c r="E161" t="n">
-        <v>5.11338865633</v>
+        <v>5.267036398017444</v>
       </c>
       <c r="F161" t="n">
-        <v>0.00594085689721</v>
+        <v>0.005957867498595963</v>
       </c>
       <c r="G161" t="n">
-        <v>0.156128084229</v>
+        <v>0.1566123366464856</v>
       </c>
       <c r="H161" t="n">
-        <v>-0.1341305495552447</v>
+        <v>-0.1236955354637637</v>
       </c>
     </row>
     <row r="162">
@@ -5596,19 +5596,19 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>-4.28382518343</v>
+        <v>-3.280201730681809</v>
       </c>
       <c r="E162" t="n">
-        <v>5.61603175997</v>
+        <v>5.745753032706924</v>
       </c>
       <c r="F162" t="n">
-        <v>0.018137142973</v>
+        <v>0.0183147137033418</v>
       </c>
       <c r="G162" t="n">
-        <v>0.175419683691</v>
+        <v>0.1772812703351182</v>
       </c>
       <c r="H162" t="n">
-        <v>0.4068873267492057</v>
+        <v>0.4085647096859546</v>
       </c>
     </row>
     <row r="163">
@@ -5628,19 +5628,19 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>-1.89027675227</v>
+        <v>-1.665572974266549</v>
       </c>
       <c r="E163" t="n">
-        <v>2.47331376209</v>
+        <v>2.616058225201634</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0822197321961</v>
+        <v>0.08237888886515311</v>
       </c>
       <c r="G163" t="n">
-        <v>0.125625959083</v>
+        <v>0.1259234263576648</v>
       </c>
       <c r="H163" t="n">
-        <v>0.02241993610159199</v>
+        <v>0.02350157415509369</v>
       </c>
     </row>
     <row r="164">
@@ -5660,19 +5660,19 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>-0.943475224075</v>
+        <v>-1.038572008346239</v>
       </c>
       <c r="E164" t="n">
-        <v>2.77521619556</v>
+        <v>2.896557993720639</v>
       </c>
       <c r="F164" t="n">
-        <v>0.000835931032755</v>
+        <v>0.0008345293532135868</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0022906266899</v>
+        <v>0.002288852691068525</v>
       </c>
       <c r="H164" t="n">
-        <v>0.3109884891197012</v>
+        <v>0.304615052263979</v>
       </c>
     </row>
     <row r="165">
@@ -5692,19 +5692,19 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>-0.391347388242</v>
+        <v>-0.8673684733816911</v>
       </c>
       <c r="E165" t="n">
-        <v>1.70233972232</v>
+        <v>1.833328022694958</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0388477102742</v>
+        <v>0.03864173919989351</v>
       </c>
       <c r="G165" t="n">
-        <v>0.0674104060076</v>
+        <v>0.06709707691652578</v>
       </c>
       <c r="H165" t="n">
-        <v>0.5873745739320535</v>
+        <v>0.5815740645650935</v>
       </c>
     </row>
     <row r="166">
@@ -5724,19 +5724,19 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>-0.503885740441</v>
+        <v>-0.8215609136698943</v>
       </c>
       <c r="E166" t="n">
-        <v>1.10250526166</v>
+        <v>1.240230258590769</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0479293616519</v>
+        <v>0.04774268910176235</v>
       </c>
       <c r="G166" t="n">
-        <v>0.0100715629596</v>
+        <v>0.01004092606935626</v>
       </c>
       <c r="H166" t="n">
-        <v>0.07085152570540654</v>
+        <v>0.05999807942962398</v>
       </c>
     </row>
     <row r="167">
@@ -5756,19 +5756,19 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>-0.249528751782</v>
+        <v>-0.5886015336662553</v>
       </c>
       <c r="E167" t="n">
-        <v>1.06238947502</v>
+        <v>1.19465566733814</v>
       </c>
       <c r="F167" t="n">
-        <v>0.014046946184</v>
+        <v>0.01399157415708934</v>
       </c>
       <c r="G167" t="n">
-        <v>0.0142442326338</v>
+        <v>0.0141975614761886</v>
       </c>
       <c r="H167" t="n">
-        <v>0.1737265511294162</v>
+        <v>0.1690643035874073</v>
       </c>
     </row>
     <row r="168">
@@ -5788,19 +5788,19 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.0627909536762</v>
+        <v>-0.5151051839775378</v>
       </c>
       <c r="E168" t="n">
-        <v>1.14158260647</v>
+        <v>1.273303626055267</v>
       </c>
       <c r="F168" t="n">
-        <v>0.00674746076202</v>
+        <v>0.006705162985362412</v>
       </c>
       <c r="G168" t="n">
-        <v>0.00558377771469</v>
+        <v>0.005552235146776378</v>
       </c>
       <c r="H168" t="n">
-        <v>0.4967582976285856</v>
+        <v>0.4872947724119614</v>
       </c>
     </row>
     <row r="169">
@@ -5820,19 +5820,19 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>-1.15131808145</v>
+        <v>-1.170276531558756</v>
       </c>
       <c r="E169" t="n">
-        <v>0.894903237387</v>
+        <v>1.023924379704355</v>
       </c>
       <c r="F169" t="n">
-        <v>0.0584284328155</v>
+        <v>0.05838224710747805</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0517948853465</v>
+        <v>0.05179219725477141</v>
       </c>
       <c r="H169" t="n">
-        <v>-0.7796807914285941</v>
+        <v>-0.7806714995404085</v>
       </c>
     </row>
     <row r="170">
@@ -5852,19 +5852,19 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>-0.230660532452</v>
+        <v>-0.5140325855067074</v>
       </c>
       <c r="E170" t="n">
-        <v>0.986725487165</v>
+        <v>1.118478675590251</v>
       </c>
       <c r="F170" t="n">
-        <v>0.0443126966678</v>
+        <v>0.04416470094569163</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0248910601528</v>
+        <v>0.02482353461466876</v>
       </c>
       <c r="H170" t="n">
-        <v>0.1156334524407443</v>
+        <v>0.1112439928079745</v>
       </c>
     </row>
     <row r="171">
@@ -5884,19 +5884,19 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>-0.301928878553</v>
+        <v>-0.6007213810462875</v>
       </c>
       <c r="E171" t="n">
-        <v>1.03569402223</v>
+        <v>1.192546765114244</v>
       </c>
       <c r="F171" t="n">
-        <v>0.0570523915653</v>
+        <v>0.05688096408940099</v>
       </c>
       <c r="G171" t="n">
-        <v>0.0650137100843</v>
+        <v>0.06481897073384146</v>
       </c>
       <c r="H171" t="n">
-        <v>0.07403393597820163</v>
+        <v>0.07307460944485644</v>
       </c>
     </row>
     <row r="172">
@@ -5916,19 +5916,19 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>-0.163713870726</v>
+        <v>-0.5977021601329402</v>
       </c>
       <c r="E172" t="n">
-        <v>1.3290006545</v>
+        <v>1.4414308106522</v>
       </c>
       <c r="F172" t="n">
-        <v>0.00205099718878</v>
+        <v>0.002040321611956743</v>
       </c>
       <c r="G172" t="n">
-        <v>0.0020500670227</v>
+        <v>0.002041610217716323</v>
       </c>
       <c r="H172" t="n">
-        <v>0.3790236822441839</v>
+        <v>0.3667196229700131</v>
       </c>
     </row>
     <row r="173">
@@ -5948,19 +5948,19 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>-0.135141861159</v>
+        <v>-0.5262109872083753</v>
       </c>
       <c r="E173" t="n">
-        <v>1.35859613793</v>
+        <v>1.520738171312019</v>
       </c>
       <c r="F173" t="n">
-        <v>0.00554674330296</v>
+        <v>0.005525485185240759</v>
       </c>
       <c r="G173" t="n">
-        <v>0.00237189502931</v>
+        <v>0.002362554782107807</v>
       </c>
       <c r="H173" t="n">
-        <v>0.3667927560960571</v>
+        <v>0.3647010748899948</v>
       </c>
     </row>
     <row r="174">
@@ -5980,10 +5980,10 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0.337916573023</v>
+        <v>-0.5090137968665087</v>
       </c>
       <c r="E174" t="n">
-        <v>1.20452504046</v>
+        <v>1.38934954763732</v>
       </c>
       <c r="F174" t="n">
         <v>0</v>
@@ -5992,7 +5992,7 @@
         <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>0.7215668203442993</v>
+        <v>0.7374828560030133</v>
       </c>
     </row>
     <row r="175">
@@ -6012,19 +6012,19 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>-0.38819927038</v>
+        <v>-0.5299721254486967</v>
       </c>
       <c r="E175" t="n">
-        <v>1.06908449467</v>
+        <v>1.193878907152146</v>
       </c>
       <c r="F175" t="n">
-        <v>0.0467630739528</v>
+        <v>0.04666405178526664</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0213249168934</v>
+        <v>0.02129820049563206</v>
       </c>
       <c r="H175" t="n">
-        <v>-0.03471820211512489</v>
+        <v>-0.03901412825867423</v>
       </c>
     </row>
     <row r="176">
@@ -6044,19 +6044,19 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>-1.13981265616</v>
+        <v>-1.113634413866882</v>
       </c>
       <c r="E176" t="n">
-        <v>1.29101240282</v>
+        <v>1.418373669018691</v>
       </c>
       <c r="F176" t="n">
-        <v>0.0307387591494</v>
+        <v>0.03072716678563575</v>
       </c>
       <c r="G176" t="n">
-        <v>0.0427423646289</v>
+        <v>0.04275983621111992</v>
       </c>
       <c r="H176" t="n">
-        <v>-0.6679955899973389</v>
+        <v>-0.6687782399580677</v>
       </c>
     </row>
     <row r="177">
@@ -6076,19 +6076,19 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>-1.17250394324</v>
+        <v>-1.110798248892952</v>
       </c>
       <c r="E177" t="n">
-        <v>0.724962598488</v>
+        <v>0.7968388523434733</v>
       </c>
       <c r="F177" t="n">
-        <v>0.00165613318044</v>
+        <v>0.001654317993848462</v>
       </c>
       <c r="G177" t="n">
-        <v>0.00142419421077</v>
+        <v>0.001425687917330035</v>
       </c>
       <c r="H177" t="n">
-        <v>-1.205532578997326</v>
+        <v>-1.20284242978258</v>
       </c>
     </row>
     <row r="178">
@@ -6108,19 +6108,19 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>-0.601474762111</v>
+        <v>-0.6741150093743986</v>
       </c>
       <c r="E178" t="n">
-        <v>1.14184867488</v>
+        <v>1.268780075748777</v>
       </c>
       <c r="F178" t="n">
-        <v>0.0253316479074</v>
+        <v>0.02529660628829165</v>
       </c>
       <c r="G178" t="n">
-        <v>0.0101129616827</v>
+        <v>0.01010720152797788</v>
       </c>
       <c r="H178" t="n">
-        <v>0.001661258916429986</v>
+        <v>-0.0004598093311214413</v>
       </c>
     </row>
     <row r="179">
@@ -6140,19 +6140,19 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>-0.372691905331</v>
+        <v>-0.3865451560148281</v>
       </c>
       <c r="E179" t="n">
-        <v>1.23065973641</v>
+        <v>1.365563275917325</v>
       </c>
       <c r="F179" t="n">
-        <v>0.0158272534856</v>
+        <v>0.01581677379431314</v>
       </c>
       <c r="G179" t="n">
-        <v>0.0128983927796</v>
+        <v>0.01289808041056732</v>
       </c>
       <c r="H179" t="n">
-        <v>-0.1040346241605206</v>
+        <v>-0.1054343472421393</v>
       </c>
     </row>
     <row r="180">
@@ -6172,19 +6172,19 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>-1.11516395155</v>
+        <v>-1.18421534532791</v>
       </c>
       <c r="E180" t="n">
-        <v>1.34604986057</v>
+        <v>1.503723947337376</v>
       </c>
       <c r="F180" t="n">
-        <v>0.0614731728646</v>
+        <v>0.0614302514897449</v>
       </c>
       <c r="G180" t="n">
-        <v>0.008142328684370001</v>
+        <v>0.008136642708722219</v>
       </c>
       <c r="H180" t="n">
-        <v>-0.07440926527940706</v>
+        <v>-0.0770516625912987</v>
       </c>
     </row>
     <row r="181">
@@ -6204,19 +6204,19 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>-0.178152274361</v>
+        <v>-0.184200490179387</v>
       </c>
       <c r="E181" t="n">
-        <v>0.234029112698</v>
+        <v>0.2626987915535173</v>
       </c>
       <c r="F181" t="n">
-        <v>0.00415207736247</v>
+        <v>0.004141633864642358</v>
       </c>
       <c r="G181" t="n">
-        <v>0.00253290606446</v>
+        <v>0.002534370098949423</v>
       </c>
       <c r="H181" t="n">
-        <v>-0.02695291515293352</v>
+        <v>-0.02756946123939619</v>
       </c>
     </row>
     <row r="182">
@@ -6236,19 +6236,19 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>-1.21641142072</v>
+        <v>-1.348159842624252</v>
       </c>
       <c r="E182" t="n">
-        <v>2.5611251719</v>
+        <v>2.703516351742574</v>
       </c>
       <c r="F182" t="n">
-        <v>0.0106756729032</v>
+        <v>0.01065792143554461</v>
       </c>
       <c r="G182" t="n">
-        <v>0.0120755755854</v>
+        <v>0.01206047457281609</v>
       </c>
       <c r="H182" t="n">
-        <v>0.4312403937658971</v>
+        <v>0.4287483774902734</v>
       </c>
     </row>
     <row r="183">
@@ -6268,19 +6268,19 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>-0.6813809376710001</v>
+        <v>-0.7965030186315669</v>
       </c>
       <c r="E183" t="n">
-        <v>1.19306949544</v>
+        <v>1.287529284281796</v>
       </c>
       <c r="F183" t="n">
-        <v>0.00737182707501</v>
+        <v>0.007354400304049376</v>
       </c>
       <c r="G183" t="n">
-        <v>0.0134364895527</v>
+        <v>0.01342503635463372</v>
       </c>
       <c r="H183" t="n">
-        <v>-0.04510947527400777</v>
+        <v>-0.04886371583078253</v>
       </c>
     </row>
     <row r="184">
@@ -6300,19 +6300,19 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0.0367009698679</v>
+        <v>-0.0417945255439478</v>
       </c>
       <c r="E184" t="n">
-        <v>1.57851613356</v>
+        <v>1.65510545186236</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0371393436206</v>
+        <v>0.03705240838857382</v>
       </c>
       <c r="G184" t="n">
-        <v>0.0204935039867</v>
+        <v>0.02048570155948893</v>
       </c>
       <c r="H184" t="n">
-        <v>0.2658173135487552</v>
+        <v>0.2616192846550236</v>
       </c>
     </row>
     <row r="185">
@@ -6332,19 +6332,19 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>-0.000162737343279</v>
+        <v>-0.1830470684880181</v>
       </c>
       <c r="E185" t="n">
-        <v>0.689495374117</v>
+        <v>0.7517772025090741</v>
       </c>
       <c r="F185" t="n">
-        <v>0.00255077312564</v>
+        <v>0.002541566468437108</v>
       </c>
       <c r="G185" t="n">
-        <v>0.00448155168241</v>
+        <v>0.004475446050442687</v>
       </c>
       <c r="H185" t="n">
-        <v>0.006442339123258201</v>
+        <v>-0.001240800596458147</v>
       </c>
     </row>
     <row r="186">
@@ -6364,19 +6364,19 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>0.0906441007331</v>
+        <v>-0.05358471609968607</v>
       </c>
       <c r="E186" t="n">
-        <v>0.773069002521</v>
+        <v>0.8501346388310793</v>
       </c>
       <c r="F186" t="n">
-        <v>0.000851535322506</v>
+        <v>0.0008490293129947509</v>
       </c>
       <c r="G186" t="n">
-        <v>0.00768680974588</v>
+        <v>0.007678746682700159</v>
       </c>
       <c r="H186" t="n">
-        <v>0.1063680814090473</v>
+        <v>0.1009699714375589</v>
       </c>
     </row>
     <row r="187">
@@ -6396,19 +6396,19 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>-0.248637048716</v>
+        <v>-0.5836858389544952</v>
       </c>
       <c r="E187" t="n">
-        <v>1.59609414923</v>
+        <v>1.699819829267613</v>
       </c>
       <c r="F187" t="n">
-        <v>0.000121732243889</v>
+        <v>0.0001212000463661042</v>
       </c>
       <c r="G187" t="n">
-        <v>0.000116709600612</v>
+        <v>0.0001163486616194787</v>
       </c>
       <c r="H187" t="n">
-        <v>0.3149249258172171</v>
+        <v>0.3028805891541753</v>
       </c>
     </row>
     <row r="188">
@@ -6428,19 +6428,19 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.0873955936386</v>
+        <v>-0.5763777210179621</v>
       </c>
       <c r="E188" t="n">
-        <v>1.29477130155</v>
+        <v>1.466017081228044</v>
       </c>
       <c r="F188" t="n">
-        <v>0.0012816861623</v>
+        <v>0.001273512914156685</v>
       </c>
       <c r="G188" t="n">
-        <v>0.000664490601183</v>
+        <v>0.0006600392545749019</v>
       </c>
       <c r="H188" t="n">
-        <v>0.530433531584662</v>
+        <v>0.5383543284933401</v>
       </c>
     </row>
     <row r="189">
@@ -6460,19 +6460,19 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0.0375783967947</v>
+        <v>-0.4258207812851467</v>
       </c>
       <c r="E189" t="n">
-        <v>1.18040992206</v>
+        <v>1.280262629785223</v>
       </c>
       <c r="F189" t="n">
-        <v>0.0009946711569100001</v>
+        <v>0.000988986110362621</v>
       </c>
       <c r="G189" t="n">
-        <v>0.000404882484298</v>
+        <v>0.0004031220007731066</v>
       </c>
       <c r="H189" t="n">
-        <v>0.3498864951522185</v>
+        <v>0.336821127162712</v>
       </c>
     </row>
     <row r="190">
@@ -6492,19 +6492,19 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.231376652561</v>
+        <v>-0.2088317041168741</v>
       </c>
       <c r="E190" t="n">
-        <v>0.977590118403</v>
+        <v>1.037231523685334</v>
       </c>
       <c r="F190" t="n">
-        <v>3.74093324395e-06</v>
+        <v>3.717686984038262e-06</v>
       </c>
       <c r="G190" t="n">
-        <v>1.44243201417e-06</v>
+        <v>1.436789406384284e-06</v>
       </c>
       <c r="H190" t="n">
-        <v>0.3985730367517926</v>
+        <v>0.3780370810213318</v>
       </c>
     </row>
     <row r="191">
@@ -6524,19 +6524,19 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0.0418240580882</v>
+        <v>-0.6050323698252869</v>
       </c>
       <c r="E191" t="n">
-        <v>1.1135111458</v>
+        <v>1.247640961738394</v>
       </c>
       <c r="F191" t="n">
-        <v>0.00035992403024</v>
+        <v>0.0003574396874054655</v>
       </c>
       <c r="G191" t="n">
-        <v>0.000989266883923</v>
+        <v>0.0009829817396035953</v>
       </c>
       <c r="H191" t="n">
-        <v>0.5102724792114932</v>
+        <v>0.5013021537801698</v>
       </c>
     </row>
     <row r="192">
@@ -6556,19 +6556,19 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>0.182331917973</v>
+        <v>-0.5267225251101126</v>
       </c>
       <c r="E192" t="n">
-        <v>1.19254128428</v>
+        <v>1.326966542923702</v>
       </c>
       <c r="F192" t="n">
-        <v>0.000370814891514</v>
+        <v>0.0003680307855342616</v>
       </c>
       <c r="G192" t="n">
-        <v>0.000747806648268</v>
+        <v>0.0007425979423285223</v>
       </c>
       <c r="H192" t="n">
-        <v>0.6292550971932931</v>
+        <v>0.623004422224227</v>
       </c>
     </row>
     <row r="193">
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1.20890306643</v>
+        <v>-0.05676541242395361</v>
       </c>
       <c r="E193" t="n">
         <v>0</v>
@@ -6600,7 +6600,7 @@
         <v>0</v>
       </c>
       <c r="H193" t="n">
-        <v>0.5515061544128841</v>
+        <v>0.4907246557880773</v>
       </c>
     </row>
     <row r="194">
@@ -6620,19 +6620,19 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>8.997760455910001</v>
+        <v>8.393244612220574</v>
       </c>
       <c r="E194" t="n">
-        <v>4.34096206322</v>
+        <v>4.296314708649973</v>
       </c>
       <c r="F194" t="n">
-        <v>0.205833241685</v>
+        <v>0.2045479368751317</v>
       </c>
       <c r="G194" t="n">
-        <v>0.206385178407</v>
+        <v>0.2052878640419434</v>
       </c>
       <c r="H194" t="n">
-        <v>2.66585393453338</v>
+        <v>1.145988676847076</v>
       </c>
     </row>
     <row r="195">
@@ -6652,19 +6652,19 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>-0.960645367314</v>
+        <v>-0.9857151736087033</v>
       </c>
       <c r="E195" t="n">
-        <v>1.69606335944</v>
+        <v>1.651424887439923</v>
       </c>
       <c r="F195" t="n">
-        <v>0.00109917618478</v>
+        <v>0.001098299325949038</v>
       </c>
       <c r="G195" t="n">
-        <v>0.000354592490451</v>
+        <v>0.0003545886299705474</v>
       </c>
       <c r="H195" t="n">
-        <v>-0.1403326995086496</v>
+        <v>0.1077508601207366</v>
       </c>
     </row>
     <row r="196">
@@ -6684,19 +6684,19 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>-2.66069771565</v>
+        <v>-2.902539442032059</v>
       </c>
       <c r="E196" t="n">
-        <v>3.73950947204</v>
+        <v>3.690208857988209</v>
       </c>
       <c r="F196" t="n">
-        <v>0.00129524340198</v>
+        <v>0.001291530746108682</v>
       </c>
       <c r="G196" t="n">
-        <v>0.0140847013895</v>
+        <v>0.01405290806071253</v>
       </c>
       <c r="H196" t="n">
-        <v>-0.4377653855330954</v>
+        <v>-0.8600089495074736</v>
       </c>
     </row>
     <row r="197">
@@ -6716,19 +6716,19 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>6.9692026727</v>
+        <v>7.488029992922129</v>
       </c>
       <c r="E197" t="n">
-        <v>1.5342425028</v>
+        <v>1.507355256344534</v>
       </c>
       <c r="F197" t="n">
-        <v>1.1092210964</v>
+        <v>1.113660617829094</v>
       </c>
       <c r="G197" t="n">
-        <v>0.08180118422840001</v>
+        <v>0.08220332540229901</v>
       </c>
       <c r="H197" t="n">
-        <v>-0.3942023872482325</v>
+        <v>-0.5432135274814121</v>
       </c>
     </row>
     <row r="198">
@@ -6748,19 +6748,19 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>5.98039943722</v>
+        <v>5.483835176607976</v>
       </c>
       <c r="E198" t="n">
-        <v>4.99485603682</v>
+        <v>4.953776461564763</v>
       </c>
       <c r="F198" t="n">
-        <v>0.204979513319</v>
+        <v>0.2039061542716373</v>
       </c>
       <c r="G198" t="n">
-        <v>0.429358327038</v>
+        <v>0.4273867080213565</v>
       </c>
       <c r="H198" t="n">
-        <v>3.091656916650454</v>
+        <v>1.408129084141962</v>
       </c>
     </row>
     <row r="199">
@@ -6780,19 +6780,19 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>-1.64712001824</v>
+        <v>-1.634687714260352</v>
       </c>
       <c r="E199" t="n">
-        <v>1.85952892664</v>
+        <v>1.825453777963815</v>
       </c>
       <c r="F199" t="n">
-        <v>0.257993948812</v>
+        <v>0.2578945090193899</v>
       </c>
       <c r="G199" t="n">
-        <v>0.583464226988</v>
+        <v>0.5835704723282664</v>
       </c>
       <c r="H199" t="n">
-        <v>-0.07885825762095067</v>
+        <v>0.3981047418020855</v>
       </c>
     </row>
     <row r="200">
@@ -6812,19 +6812,19 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>-1.98479978049</v>
+        <v>-1.962667247358552</v>
       </c>
       <c r="E200" t="n">
-        <v>1.92879935738</v>
+        <v>1.892691148547487</v>
       </c>
       <c r="F200" t="n">
-        <v>0.0277965443885</v>
+        <v>0.0277887964843366</v>
       </c>
       <c r="G200" t="n">
-        <v>0.0373753148382</v>
+        <v>0.03738655458343837</v>
       </c>
       <c r="H200" t="n">
-        <v>-0.788360993307291</v>
+        <v>-0.7142863859737392</v>
       </c>
     </row>
     <row r="201">
@@ -6844,19 +6844,19 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>-1.62805482652</v>
+        <v>-1.629714489004253</v>
       </c>
       <c r="E201" t="n">
-        <v>1.87345630392</v>
+        <v>1.840289939153772</v>
       </c>
       <c r="F201" t="n">
-        <v>0.118456463318</v>
+        <v>0.1184055417739206</v>
       </c>
       <c r="G201" t="n">
-        <v>0.07683750729320001</v>
+        <v>0.07684131192265747</v>
       </c>
       <c r="H201" t="n">
-        <v>-0.1308929068941533</v>
+        <v>0.01993085807681094</v>
       </c>
     </row>
     <row r="202">
@@ -6876,19 +6876,19 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>-0.888672100943</v>
+        <v>-0.8905601033168953</v>
       </c>
       <c r="E202" t="n">
-        <v>1.79033735546</v>
+        <v>1.756293706971657</v>
       </c>
       <c r="F202" t="n">
-        <v>0.00348071713718</v>
+        <v>0.003479486227515173</v>
       </c>
       <c r="G202" t="n">
-        <v>0.00334792738378</v>
+        <v>0.003348084068182071</v>
       </c>
       <c r="H202" t="n">
-        <v>-0.1490628033052444</v>
+        <v>-0.05544205403746894</v>
       </c>
     </row>
     <row r="203">
@@ -6908,19 +6908,19 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>37.7450682225</v>
+        <v>39.5358741797559</v>
       </c>
       <c r="E203" t="n">
-        <v>21.7942624086</v>
+        <v>21.7600633718466</v>
       </c>
       <c r="F203" t="n">
-        <v>0.483104079404</v>
+        <v>0.489262421021476</v>
       </c>
       <c r="G203" t="n">
-        <v>0.384276066152</v>
+        <v>0.3892884955311071</v>
       </c>
       <c r="H203" t="n">
-        <v>0.08358087420354821</v>
+        <v>-0.06775199171163981</v>
       </c>
     </row>
     <row r="204">
@@ -6940,19 +6940,19 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>-6.30464533034</v>
+        <v>-6.257436058713173</v>
       </c>
       <c r="E204" t="n">
-        <v>2.35031087021</v>
+        <v>2.320790242180237</v>
       </c>
       <c r="F204" t="n">
-        <v>0.793506698791</v>
+        <v>0.7934772920034679</v>
       </c>
       <c r="G204" t="n">
-        <v>0.274213675816</v>
+        <v>0.2743688646955434</v>
       </c>
       <c r="H204" t="n">
-        <v>-0.2141098458570356</v>
+        <v>-0.2600681028507745</v>
       </c>
     </row>
     <row r="205">
@@ -6972,19 +6972,19 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>-0.940609604735</v>
+        <v>-0.9850266155903009</v>
       </c>
       <c r="E205" t="n">
-        <v>1.51876096894</v>
+        <v>1.489522691299938</v>
       </c>
       <c r="F205" t="n">
-        <v>0.123527976306</v>
+        <v>0.1234251269345663</v>
       </c>
       <c r="G205" t="n">
-        <v>0.0288864583221</v>
+        <v>0.02887516223148937</v>
       </c>
       <c r="H205" t="n">
-        <v>-0.01056659063556342</v>
+        <v>0.1119525696760659</v>
       </c>
     </row>
     <row r="206">
@@ -7004,19 +7004,19 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>-2.59033503643</v>
+        <v>-2.554893415865678</v>
       </c>
       <c r="E206" t="n">
-        <v>2.10870143221</v>
+        <v>2.076375713059475</v>
       </c>
       <c r="F206" t="n">
-        <v>0.178435122935</v>
+        <v>0.1784274947193125</v>
       </c>
       <c r="G206" t="n">
-        <v>0.206588900044</v>
+        <v>0.2066750520952428</v>
       </c>
       <c r="H206" t="n">
-        <v>-0.6142226199257195</v>
+        <v>-0.5273983612194</v>
       </c>
     </row>
     <row r="207">
@@ -7036,19 +7036,19 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>-1.89741869021</v>
+        <v>-1.823010633578204</v>
       </c>
       <c r="E207" t="n">
-        <v>2.56195493742</v>
+        <v>2.528704809471627</v>
       </c>
       <c r="F207" t="n">
-        <v>0.142280587204</v>
+        <v>0.1423385071997572</v>
       </c>
       <c r="G207" t="n">
-        <v>0.141415096712</v>
+        <v>0.141530800257833</v>
       </c>
       <c r="H207" t="n">
-        <v>-0.8057246806684737</v>
+        <v>-0.7382104365376785</v>
       </c>
     </row>
     <row r="208">
@@ -7068,19 +7068,19 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>-4.14521152959</v>
+        <v>-4.085567576070281</v>
       </c>
       <c r="E208" t="n">
-        <v>1.61999735468</v>
+        <v>1.591380347067695</v>
       </c>
       <c r="F208" t="n">
-        <v>1.36517429586</v>
+        <v>1.365402097495085</v>
       </c>
       <c r="G208" t="n">
-        <v>0.492024223769</v>
+        <v>0.4923557975366994</v>
       </c>
       <c r="H208" t="n">
-        <v>-1.173971569367693</v>
+        <v>-1.094418003198627</v>
       </c>
     </row>
     <row r="209">
@@ -7100,19 +7100,19 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>-2.43273467055</v>
+        <v>-2.397098759281469</v>
       </c>
       <c r="E209" t="n">
-        <v>1.63239453105</v>
+        <v>1.60033236962196</v>
       </c>
       <c r="F209" t="n">
-        <v>0.210538391547</v>
+        <v>0.2105236218295613</v>
       </c>
       <c r="G209" t="n">
-        <v>0.273843748348</v>
+        <v>0.2739578506749873</v>
       </c>
       <c r="H209" t="n">
-        <v>-1.089949675067692</v>
+        <v>-1.016442168128906</v>
       </c>
     </row>
     <row r="210">
@@ -7132,19 +7132,19 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>-2.19646560904</v>
+        <v>-2.212072586508929</v>
       </c>
       <c r="E210" t="n">
-        <v>1.35041993797</v>
+        <v>1.323829626046535</v>
       </c>
       <c r="F210" t="n">
-        <v>0.419893619372</v>
+        <v>0.4196207394285047</v>
       </c>
       <c r="G210" t="n">
-        <v>0.07041870303809999</v>
+        <v>0.07041093318186947</v>
       </c>
       <c r="H210" t="n">
-        <v>-0.9364998936353786</v>
+        <v>-0.8241648043558647</v>
       </c>
     </row>
     <row r="211">
@@ -7164,19 +7164,19 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>-2.9229358611</v>
+        <v>-2.907049123659922</v>
       </c>
       <c r="E211" t="n">
-        <v>1.64951803581</v>
+        <v>1.618661935496957</v>
       </c>
       <c r="F211" t="n">
-        <v>0.391607969071</v>
+        <v>0.3914316097836967</v>
       </c>
       <c r="G211" t="n">
-        <v>0.331568731464</v>
+        <v>0.3316396910980877</v>
       </c>
       <c r="H211" t="n">
-        <v>-0.7999500117542357</v>
+        <v>-0.6247915760197675</v>
       </c>
     </row>
     <row r="212">
@@ -7196,19 +7196,19 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>-3.29658201023</v>
+        <v>-3.239452452720026</v>
       </c>
       <c r="E212" t="n">
-        <v>1.54837719317</v>
+        <v>1.519452242248032</v>
       </c>
       <c r="F212" t="n">
-        <v>0.624638776453</v>
+        <v>0.6246720479196021</v>
       </c>
       <c r="G212" t="n">
-        <v>0.324203091785</v>
+        <v>0.3244102194888546</v>
       </c>
       <c r="H212" t="n">
-        <v>-1.33130873316778</v>
+        <v>-1.347532178408306</v>
       </c>
     </row>
     <row r="213">
@@ -7228,19 +7228,19 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>-3.032648978</v>
+        <v>-3.018508374070261</v>
       </c>
       <c r="E213" t="n">
-        <v>1.66017384052</v>
+        <v>1.629618132783883</v>
       </c>
       <c r="F213" t="n">
-        <v>0.867633541427</v>
+        <v>0.867354607037551</v>
       </c>
       <c r="G213" t="n">
-        <v>0.585200570659</v>
+        <v>0.5853177416187126</v>
       </c>
       <c r="H213" t="n">
-        <v>-0.9808385696685851</v>
+        <v>-0.8112119276099561</v>
       </c>
     </row>
     <row r="214">
@@ -7260,19 +7260,19 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>-2.45956022519</v>
+        <v>-2.402722492298459</v>
       </c>
       <c r="E214" t="n">
-        <v>1.485035615</v>
+        <v>1.452503375590775</v>
       </c>
       <c r="F214" t="n">
-        <v>0.171905366126</v>
+        <v>0.1718871284321722</v>
       </c>
       <c r="G214" t="n">
-        <v>0.138745537194</v>
+        <v>0.1388349805313238</v>
       </c>
       <c r="H214" t="n">
-        <v>-1.417074859791201</v>
+        <v>-1.37658564078561</v>
       </c>
     </row>
     <row r="215">
@@ -7292,19 +7292,19 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>-1.19171477387</v>
+        <v>-1.269455039360146</v>
       </c>
       <c r="E215" t="n">
-        <v>1.61830868181</v>
+        <v>1.584517658432505</v>
       </c>
       <c r="F215" t="n">
-        <v>0.106506149954</v>
+        <v>0.1063673379598154</v>
       </c>
       <c r="G215" t="n">
-        <v>0.171311459852</v>
+        <v>0.1711866090808874</v>
       </c>
       <c r="H215" t="n">
-        <v>-0.277300675953962</v>
+        <v>0.1089552805332739</v>
       </c>
     </row>
     <row r="216">
@@ -7324,19 +7324,19 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>-2.27406619127</v>
+        <v>-2.036022591828957</v>
       </c>
       <c r="E216" t="n">
-        <v>1.64597598313</v>
+        <v>1.613864292592115</v>
       </c>
       <c r="F216" t="n">
-        <v>0.0346680600905</v>
+        <v>0.03473874551014868</v>
       </c>
       <c r="G216" t="n">
-        <v>0.0520620603156</v>
+        <v>0.0521915684379359</v>
       </c>
       <c r="H216" t="n">
-        <v>-0.9348749684492952</v>
+        <v>-0.8574526672226357</v>
       </c>
     </row>
     <row r="217">
@@ -7356,19 +7356,19 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1.61821054446</v>
+        <v>1.311476012165391</v>
       </c>
       <c r="E217" t="n">
-        <v>2.31950952986</v>
+        <v>2.284429195715787</v>
       </c>
       <c r="F217" t="n">
-        <v>0.0129249224057</v>
+        <v>0.01288162673789522</v>
       </c>
       <c r="G217" t="n">
-        <v>0.00762381779025</v>
+        <v>0.00760134569760672</v>
       </c>
       <c r="H217" t="n">
-        <v>0.5032188671066695</v>
+        <v>0.1585613350820303</v>
       </c>
     </row>
     <row r="218">
@@ -7388,19 +7388,19 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>-0.141264040998</v>
+        <v>-0.1824055664338853</v>
       </c>
       <c r="E218" t="n">
-        <v>1.747919527</v>
+        <v>1.719635531511154</v>
       </c>
       <c r="F218" t="n">
-        <v>7.281857889240001e-05</v>
+        <v>7.277777473289108e-05</v>
       </c>
       <c r="G218" t="n">
-        <v>5.88345877405e-05</v>
+        <v>5.881222016125937e-05</v>
       </c>
       <c r="H218" t="n">
-        <v>0.0693919065163584</v>
+        <v>0.3054509572895103</v>
       </c>
     </row>
     <row r="219">
@@ -7420,19 +7420,19 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>-3.24692977937</v>
+        <v>-3.192415062370446</v>
       </c>
       <c r="E219" t="n">
-        <v>1.56301605753</v>
+        <v>1.532480515641721</v>
       </c>
       <c r="F219" t="n">
-        <v>0.21222187739</v>
+        <v>0.2122593368986363</v>
       </c>
       <c r="G219" t="n">
-        <v>0.021080269029</v>
+        <v>0.02109374387629172</v>
       </c>
       <c r="H219" t="n">
-        <v>-0.8341013261619845</v>
+        <v>-0.7561887774145681</v>
       </c>
     </row>
     <row r="220">
@@ -7452,19 +7452,19 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>-2.20083732188</v>
+        <v>-2.167367343871329</v>
       </c>
       <c r="E220" t="n">
-        <v>2.11829662465</v>
+        <v>2.085639146984786</v>
       </c>
       <c r="F220" t="n">
-        <v>0.06694389123570001</v>
+        <v>0.06695453533768825</v>
       </c>
       <c r="G220" t="n">
-        <v>0.0402105911186</v>
+        <v>0.04022665708620072</v>
       </c>
       <c r="H220" t="n">
-        <v>-1.333403802294375</v>
+        <v>-1.302595011165719</v>
       </c>
     </row>
     <row r="221">
@@ -7484,19 +7484,19 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>-0.75870992468</v>
+        <v>-0.7556575239674568</v>
       </c>
       <c r="E221" t="n">
-        <v>1.7667868922</v>
+        <v>1.72678381315281</v>
       </c>
       <c r="F221" t="n">
-        <v>0.00606421676171</v>
+        <v>0.006062387473039462</v>
       </c>
       <c r="G221" t="n">
-        <v>0.121681614579</v>
+        <v>0.1216943512545913</v>
       </c>
       <c r="H221" t="n">
-        <v>-0.1870858836923395</v>
+        <v>0.06495681505627182</v>
       </c>
     </row>
     <row r="222">
@@ -7516,19 +7516,19 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>-0.981989346606</v>
+        <v>-0.8969246421838051</v>
       </c>
       <c r="E222" t="n">
-        <v>2.28968797871</v>
+        <v>2.253459066451269</v>
       </c>
       <c r="F222" t="n">
-        <v>0.0702307213721</v>
+        <v>0.07027243367510189</v>
       </c>
       <c r="G222" t="n">
-        <v>0.457790648049</v>
+        <v>0.4582091666684362</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.1696637597206729</v>
+        <v>0.001987486142684958</v>
       </c>
     </row>
     <row r="223">
@@ -7548,19 +7548,19 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>-0.549914378155</v>
+        <v>-0.5976851896614011</v>
       </c>
       <c r="E223" t="n">
-        <v>1.62606148585</v>
+        <v>1.590828871793226</v>
       </c>
       <c r="F223" t="n">
-        <v>0.0120966109121</v>
+        <v>0.01208786124972641</v>
       </c>
       <c r="G223" t="n">
-        <v>0.378679982639</v>
+        <v>0.3785173283206771</v>
       </c>
       <c r="H223" t="n">
-        <v>-0.1506879854298426</v>
+        <v>0.03003336179365768</v>
       </c>
     </row>
     <row r="224">
@@ -7580,19 +7580,19 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>-2.03495965011</v>
+        <v>-1.589622296628812</v>
       </c>
       <c r="E224" t="n">
-        <v>3.98672346722</v>
+        <v>3.942154947545684</v>
       </c>
       <c r="F224" t="n">
-        <v>0.0324978666302</v>
+        <v>0.0326321799956955</v>
       </c>
       <c r="G224" t="n">
-        <v>0.465870712283</v>
+        <v>0.4680282721555536</v>
       </c>
       <c r="H224" t="n">
-        <v>-0.2450483521835634</v>
+        <v>0.02308680502822735</v>
       </c>
     </row>
     <row r="225">
@@ -7612,19 +7612,19 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>-2.69434681163</v>
+        <v>-2.205116550942809</v>
       </c>
       <c r="E225" t="n">
-        <v>5.43844788853</v>
+        <v>5.373938775570108</v>
       </c>
       <c r="F225" t="n">
-        <v>0.00593327130647</v>
+        <v>0.005957766177570152</v>
       </c>
       <c r="G225" t="n">
-        <v>0.155741152693</v>
+        <v>0.1565373242725939</v>
       </c>
       <c r="H225" t="n">
-        <v>-0.3713472023795905</v>
+        <v>-0.1675793627433309</v>
       </c>
     </row>
     <row r="226">
@@ -7644,19 +7644,19 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>-4.73866398104</v>
+        <v>-3.322735012897238</v>
       </c>
       <c r="E226" t="n">
-        <v>5.86244974321</v>
+        <v>5.825706677817344</v>
       </c>
       <c r="F226" t="n">
-        <v>0.0180402665325</v>
+        <v>0.01830370943497052</v>
       </c>
       <c r="G226" t="n">
-        <v>0.174604956904</v>
+        <v>0.1772085168889443</v>
       </c>
       <c r="H226" t="n">
-        <v>-0.07024151788944666</v>
+        <v>0.3644092637890228</v>
       </c>
     </row>
     <row r="227">
@@ -7676,19 +7676,19 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>-2.1089984063</v>
+        <v>-1.699673878784913</v>
       </c>
       <c r="E227" t="n">
-        <v>2.73892741182</v>
+        <v>2.702004958758697</v>
       </c>
       <c r="F227" t="n">
-        <v>0.0820322609702</v>
+        <v>0.08235117769421921</v>
       </c>
       <c r="G227" t="n">
-        <v>0.125347288493</v>
+        <v>0.1258794717043066</v>
       </c>
       <c r="H227" t="n">
-        <v>-0.2005658027661839</v>
+        <v>-0.01118507608470765</v>
       </c>
     </row>
     <row r="228">
@@ -7708,19 +7708,19 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>-1.3514344073</v>
+        <v>-1.123926836290556</v>
       </c>
       <c r="E228" t="n">
-        <v>2.99894213442</v>
+        <v>2.968858055771872</v>
       </c>
       <c r="F228" t="n">
-        <v>0.000831790673201</v>
+        <v>0.0008336018719234543</v>
       </c>
       <c r="G228" t="n">
-        <v>0.00228168780754</v>
+        <v>0.00228702597398638</v>
       </c>
       <c r="H228" t="n">
-        <v>-0.1021371381429659</v>
+        <v>0.2181017173863875</v>
       </c>
     </row>
     <row r="229">
@@ -7740,19 +7740,19 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>-1.00403026959</v>
+        <v>-0.9636341107792767</v>
       </c>
       <c r="E229" t="n">
-        <v>1.94546201749</v>
+        <v>1.911957234543782</v>
       </c>
       <c r="F229" t="n">
-        <v>0.0385917351663</v>
+        <v>0.03859961690386929</v>
       </c>
       <c r="G229" t="n">
-        <v>0.06700316050629999</v>
+        <v>0.06703391668730166</v>
       </c>
       <c r="H229" t="n">
-        <v>-0.03132832852956735</v>
+        <v>0.4839013891940303</v>
       </c>
     </row>
     <row r="230">
@@ -7772,19 +7772,19 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>-0.840000270008</v>
+        <v>-0.8938882794351288</v>
       </c>
       <c r="E230" t="n">
-        <v>1.34697238078</v>
+        <v>1.318814981048444</v>
       </c>
       <c r="F230" t="n">
-        <v>0.0477331688818</v>
+        <v>0.04769804733936274</v>
       </c>
       <c r="G230" t="n">
-        <v>0.0100390883518</v>
+        <v>0.01003404768878003</v>
       </c>
       <c r="H230" t="n">
-        <v>-0.2672045625573549</v>
+        <v>-0.01297217646701876</v>
       </c>
     </row>
     <row r="231">
@@ -7804,19 +7804,19 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>-0.559699776115</v>
+        <v>-0.637012952362459</v>
       </c>
       <c r="E231" t="n">
-        <v>1.30703935148</v>
+        <v>1.273752517996685</v>
       </c>
       <c r="F231" t="n">
-        <v>0.0139972635303</v>
+        <v>0.01398318237934669</v>
       </c>
       <c r="G231" t="n">
-        <v>0.0142013172096</v>
+        <v>0.01419100952403391</v>
       </c>
       <c r="H231" t="n">
-        <v>-0.1377605725584652</v>
+        <v>0.1202839163559455</v>
       </c>
     </row>
     <row r="232">
@@ -7836,19 +7836,19 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>-0.583470212007</v>
+        <v>-0.6928019093791371</v>
       </c>
       <c r="E232" t="n">
-        <v>1.38407052264</v>
+        <v>1.351650789855019</v>
       </c>
       <c r="F232" t="n">
-        <v>0.00670102386251</v>
+        <v>0.006692410548961629</v>
       </c>
       <c r="G232" t="n">
-        <v>0.00554832035323</v>
+        <v>0.005542482446710377</v>
       </c>
       <c r="H232" t="n">
-        <v>-0.1523056705639125</v>
+        <v>0.3078075923878432</v>
       </c>
     </row>
     <row r="233">
@@ -7868,19 +7868,19 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>-1.24813037121</v>
+        <v>-1.190149590034328</v>
       </c>
       <c r="E233" t="n">
-        <v>1.13313735761</v>
+        <v>1.100929636980075</v>
       </c>
       <c r="F233" t="n">
-        <v>0.0583391598086</v>
+        <v>0.05836160092086529</v>
       </c>
       <c r="G233" t="n">
-        <v>0.0517507958904</v>
+        <v>0.05178362839195146</v>
       </c>
       <c r="H233" t="n">
-        <v>-0.8768570623394645</v>
+        <v>-0.8006229012846977</v>
       </c>
     </row>
     <row r="234">
@@ -7900,19 +7900,19 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>-0.455964429849</v>
+        <v>-0.5399310540556534</v>
       </c>
       <c r="E234" t="n">
-        <v>1.22969573722</v>
+        <v>1.196992066300973</v>
       </c>
       <c r="F234" t="n">
-        <v>0.0441941682028</v>
+        <v>0.04414823843712539</v>
       </c>
       <c r="G234" t="n">
-        <v>0.0248374949069</v>
+        <v>0.02481778425333812</v>
       </c>
       <c r="H234" t="n">
-        <v>-0.1104524626067471</v>
+        <v>0.08518275049083091</v>
       </c>
     </row>
     <row r="235">
@@ -7932,19 +7932,19 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>-0.618116051091</v>
+        <v>-0.6574011158359649</v>
       </c>
       <c r="E235" t="n">
-        <v>1.32687500081</v>
+        <v>1.286732391977607</v>
       </c>
       <c r="F235" t="n">
-        <v>0.0569070135785</v>
+        <v>0.0568616199790108</v>
       </c>
       <c r="G235" t="n">
-        <v>0.0647990932995</v>
+        <v>0.06477890581217796</v>
       </c>
       <c r="H235" t="n">
-        <v>-0.2433455827904552</v>
+        <v>0.01601066082008717</v>
       </c>
     </row>
     <row r="236">
@@ -7964,19 +7964,19 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>-0.541367377865</v>
+        <v>-0.6348910321679391</v>
       </c>
       <c r="E236" t="n">
-        <v>1.53540550795</v>
+        <v>1.508087850927797</v>
       </c>
       <c r="F236" t="n">
-        <v>0.00204095849047</v>
+        <v>0.002038865665955303</v>
       </c>
       <c r="G236" t="n">
-        <v>0.00204290161097</v>
+        <v>0.002041025536230105</v>
       </c>
       <c r="H236" t="n">
-        <v>-0.0006828533905767209</v>
+        <v>0.3291699367580891</v>
       </c>
     </row>
     <row r="237">
@@ -7996,19 +7996,19 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>-0.629915498879</v>
+        <v>-0.6536169960166816</v>
       </c>
       <c r="E237" t="n">
-        <v>1.65740254848</v>
+        <v>1.617296959393322</v>
       </c>
       <c r="F237" t="n">
-        <v>0.00552275977531</v>
+        <v>0.0055196547239051</v>
       </c>
       <c r="G237" t="n">
-        <v>0.00235975124479</v>
+        <v>0.002359388942215965</v>
       </c>
       <c r="H237" t="n">
-        <v>-0.1304676824976814</v>
+        <v>0.2361539860931128</v>
       </c>
     </row>
     <row r="238">
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>-0.52540684589</v>
+        <v>-0.6785192855012334</v>
       </c>
       <c r="E238" t="n">
-        <v>1.54702068869</v>
+        <v>1.500118464348832</v>
       </c>
       <c r="F238" t="n">
         <v>0</v>
@@ -8040,7 +8040,7 @@
         <v>0</v>
       </c>
       <c r="H238" t="n">
-        <v>-0.1450575864155312</v>
+        <v>0.5658536772503275</v>
       </c>
     </row>
     <row r="239">
@@ -8060,19 +8060,19 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>-0.5730732592460001</v>
+        <v>-0.5692569928326452</v>
       </c>
       <c r="E239" t="n">
-        <v>1.29811583363</v>
+        <v>1.267837505190683</v>
       </c>
       <c r="F239" t="n">
-        <v>0.04664100367</v>
+        <v>0.04663531782337253</v>
       </c>
       <c r="G239" t="n">
-        <v>0.0212892885604</v>
+        <v>0.02129094307278164</v>
       </c>
       <c r="H239" t="n">
-        <v>-0.2202482322794519</v>
+        <v>-0.07849289545569516</v>
       </c>
     </row>
     <row r="240">
@@ -8092,19 +8092,19 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>-1.19083656205</v>
+        <v>-1.129522984395714</v>
       </c>
       <c r="E240" t="n">
-        <v>1.52591604432</v>
+        <v>1.49428255945101</v>
       </c>
       <c r="F240" t="n">
-        <v>0.030703331825</v>
+        <v>0.03071665470131245</v>
       </c>
       <c r="G240" t="n">
-        <v>0.0427264048199</v>
+        <v>0.04275470511631839</v>
       </c>
       <c r="H240" t="n">
-        <v>-0.719263010999216</v>
+        <v>-0.6847382877694597</v>
       </c>
     </row>
     <row r="241">
@@ -8124,19 +8124,19 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>-1.07675383666</v>
+        <v>-1.07932295456562</v>
       </c>
       <c r="E241" t="n">
-        <v>0.856132777926</v>
+        <v>0.8391601474004196</v>
       </c>
       <c r="F241" t="n">
-        <v>0.00165329923474</v>
+        <v>0.001653448270823841</v>
       </c>
       <c r="G241" t="n">
-        <v>0.00142651623576</v>
+        <v>0.001426438374392607</v>
       </c>
       <c r="H241" t="n">
-        <v>-1.109814472574377</v>
+        <v>-1.171396432058247</v>
       </c>
     </row>
     <row r="242">
@@ -8156,19 +8156,19 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>-0.741185567432</v>
+        <v>-0.6988128663799942</v>
       </c>
       <c r="E242" t="n">
-        <v>1.37389566781</v>
+        <v>1.343675932659782</v>
       </c>
       <c r="F242" t="n">
-        <v>0.0252784227354</v>
+        <v>0.02528519482689788</v>
       </c>
       <c r="G242" t="n">
-        <v>0.0101004852882</v>
+        <v>0.01010519372959031</v>
       </c>
       <c r="H242" t="n">
-        <v>-0.1388972915699616</v>
+        <v>-0.02532517392855871</v>
       </c>
     </row>
     <row r="243">
@@ -8188,19 +8188,19 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>-0.389531019633</v>
+        <v>-0.3700554395985489</v>
       </c>
       <c r="E243" t="n">
-        <v>1.47903733777</v>
+        <v>1.445808391437287</v>
       </c>
       <c r="F243" t="n">
-        <v>0.0158185782904</v>
+        <v>0.01581786513823101</v>
       </c>
       <c r="G243" t="n">
-        <v>0.0128972860533</v>
+        <v>0.01290048879110602</v>
       </c>
       <c r="H243" t="n">
-        <v>-0.1209191472038795</v>
+        <v>-0.08889809657478542</v>
       </c>
     </row>
     <row r="244">
@@ -8220,19 +8220,19 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>-1.36832473444</v>
+        <v>-1.240239628594564</v>
       </c>
       <c r="E244" t="n">
-        <v>1.63149702257</v>
+        <v>1.595739435630184</v>
       </c>
       <c r="F244" t="n">
-        <v>0.0613476728699</v>
+        <v>0.06140714955917082</v>
       </c>
       <c r="G244" t="n">
-        <v>0.008120433334149999</v>
+        <v>0.008131643408593495</v>
       </c>
       <c r="H244" t="n">
-        <v>-0.3302345443823906</v>
+        <v>-0.1337036598613506</v>
       </c>
     </row>
     <row r="245">
@@ -8252,19 +8252,19 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>-0.216164630279</v>
+        <v>-0.1900399374564987</v>
       </c>
       <c r="E245" t="n">
-        <v>0.286868178117</v>
+        <v>0.2797652914338533</v>
       </c>
       <c r="F245" t="n">
-        <v>0.00413376341272</v>
+        <v>0.004136081447183516</v>
       </c>
       <c r="G245" t="n">
-        <v>0.00253459972825</v>
+        <v>0.002535066544832944</v>
       </c>
       <c r="H245" t="n">
-        <v>-0.06502284808426184</v>
+        <v>-0.03341807178164347</v>
       </c>
     </row>
     <row r="246">
@@ -8284,19 +8284,19 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>-1.76497033382</v>
+        <v>-1.428113542765863</v>
       </c>
       <c r="E246" t="n">
-        <v>2.82512237238</v>
+        <v>2.788891089694356</v>
       </c>
       <c r="F246" t="n">
-        <v>0.0106155248608</v>
+        <v>0.01064925210067435</v>
       </c>
       <c r="G246" t="n">
-        <v>0.0120087653455</v>
+        <v>0.01205070900085866</v>
       </c>
       <c r="H246" t="n">
-        <v>-0.1264681574624671</v>
+        <v>0.3473545583728255</v>
       </c>
     </row>
     <row r="247">
@@ -8316,19 +8316,19 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>-0.86672567419</v>
+        <v>-0.8444933759881423</v>
       </c>
       <c r="E247" t="n">
-        <v>1.36747236449</v>
+        <v>1.34388899630129</v>
       </c>
       <c r="F247" t="n">
-        <v>0.00734536296358</v>
+        <v>0.007346901612975156</v>
       </c>
       <c r="G247" t="n">
-        <v>0.0134173129407</v>
+        <v>0.01342037249245619</v>
       </c>
       <c r="H247" t="n">
-        <v>-0.231641598082355</v>
+        <v>-0.09721574871701666</v>
       </c>
     </row>
     <row r="248">
@@ -8348,19 +8348,19 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>-0.275577064843</v>
+        <v>-0.2814191220379292</v>
       </c>
       <c r="E248" t="n">
-        <v>1.71918057485</v>
+        <v>1.700530373923703</v>
       </c>
       <c r="F248" t="n">
-        <v>0.036935018128</v>
+        <v>0.03693585141684595</v>
       </c>
       <c r="G248" t="n">
-        <v>0.02044219808</v>
+        <v>0.0204405704080598</v>
       </c>
       <c r="H248" t="n">
-        <v>-0.04717593868562853</v>
+        <v>0.02126733004677028</v>
       </c>
     </row>
     <row r="249">
@@ -8380,19 +8380,19 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>-0.088154595526</v>
+        <v>-0.1928545440964879</v>
       </c>
       <c r="E249" t="n">
-        <v>0.804549540627</v>
+        <v>0.7889567021010402</v>
       </c>
       <c r="F249" t="n">
-        <v>0.00254139403149</v>
+        <v>0.002539071547414366</v>
       </c>
       <c r="G249" t="n">
-        <v>0.00448089428378</v>
+        <v>0.004476041468879063</v>
       </c>
       <c r="H249" t="n">
-        <v>-0.08155533099842849</v>
+        <v>-0.01106613950855317</v>
       </c>
     </row>
     <row r="250">
@@ -8412,19 +8412,19 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>-0.00160269676606</v>
+        <v>-0.07077913838936523</v>
       </c>
       <c r="E250" t="n">
-        <v>0.915063281904</v>
+        <v>0.896008839300988</v>
       </c>
       <c r="F250" t="n">
-        <v>0.000848801345687</v>
+        <v>0.000848272710741914</v>
       </c>
       <c r="G250" t="n">
-        <v>0.00768432024569</v>
+        <v>0.007678866216583658</v>
       </c>
       <c r="H250" t="n">
-        <v>0.01410679217717092</v>
+        <v>0.08374896011458244</v>
       </c>
     </row>
     <row r="251">
@@ -8444,19 +8444,19 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>-0.5335817358379999</v>
+        <v>-0.588182440295848</v>
       </c>
       <c r="E251" t="n">
-        <v>1.78761233553</v>
+        <v>1.761713342203897</v>
       </c>
       <c r="F251" t="n">
-        <v>0.000121216205092</v>
+        <v>0.0001211428810094574</v>
       </c>
       <c r="G251" t="n">
-        <v>0.000116418627732</v>
+        <v>0.0001163564325507406</v>
       </c>
       <c r="H251" t="n">
-        <v>0.02837039612508807</v>
+        <v>0.298343888400332</v>
       </c>
     </row>
     <row r="252">
@@ -8476,19 +8476,19 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>-0.549915099889</v>
+        <v>-0.6655045363519907</v>
       </c>
       <c r="E252" t="n">
-        <v>1.61195226559</v>
+        <v>1.568586968021601</v>
       </c>
       <c r="F252" t="n">
-        <v>0.00127477470198</v>
+        <v>0.001272803128197631</v>
       </c>
       <c r="G252" t="n">
-        <v>0.000660089390667</v>
+        <v>0.0006593888118307966</v>
       </c>
       <c r="H252" t="n">
-        <v>-0.1096982246133749</v>
+        <v>0.4482282283289285</v>
       </c>
     </row>
     <row r="253">
@@ -8508,19 +8508,19 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>-0.30419910995</v>
+        <v>-0.4558514218374277</v>
       </c>
       <c r="E253" t="n">
-        <v>1.36499661012</v>
+        <v>1.339926205772768</v>
       </c>
       <c r="F253" t="n">
-        <v>0.0009897743718460001</v>
+        <v>0.0009882265479901876</v>
       </c>
       <c r="G253" t="n">
-        <v>0.000403659232195</v>
+        <v>0.0004030497197496448</v>
       </c>
       <c r="H253" t="n">
-        <v>0.007041990536293952</v>
+        <v>0.3065604809483036</v>
       </c>
     </row>
     <row r="254">
@@ -8540,19 +8540,19 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>-0.06681551145509999</v>
+        <v>-0.267466429946206</v>
       </c>
       <c r="E254" t="n">
-        <v>1.08720512194</v>
+        <v>1.07263421364423</v>
       </c>
       <c r="F254" t="n">
-        <v>3.71899725796e-06</v>
+        <v>3.712100696260644e-06</v>
       </c>
       <c r="G254" t="n">
-        <v>1.4392392497e-06</v>
+        <v>1.436291364803772e-06</v>
       </c>
       <c r="H254" t="n">
-        <v>0.09988345712308444</v>
+        <v>0.3190575261765582</v>
       </c>
     </row>
     <row r="255">
@@ -8572,19 +8572,19 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>-0.592708720337</v>
+        <v>-0.7522945774324108</v>
       </c>
       <c r="E255" t="n">
-        <v>1.3602106436</v>
+        <v>1.327332422527383</v>
       </c>
       <c r="F255" t="n">
-        <v>0.000357520875578</v>
+        <v>0.0003568788346981795</v>
       </c>
       <c r="G255" t="n">
-        <v>0.0009830774894389999</v>
+        <v>0.0009815475319113484</v>
       </c>
       <c r="H255" t="n">
-        <v>-0.127231515312598</v>
+        <v>0.3524008162635317</v>
       </c>
     </row>
     <row r="256">
@@ -8604,19 +8604,19 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>-0.486308026501</v>
+        <v>-0.6578043589827276</v>
       </c>
       <c r="E256" t="n">
-        <v>1.441204355</v>
+        <v>1.407354483572631</v>
       </c>
       <c r="F256" t="n">
-        <v>0.000368229039509</v>
+        <v>0.0003675181595484701</v>
       </c>
       <c r="G256" t="n">
-        <v>0.000742873999132</v>
+        <v>0.0007416339332107675</v>
       </c>
       <c r="H256" t="n">
-        <v>-0.04236771545733653</v>
+        <v>0.4904075250045992</v>
       </c>
     </row>
     <row r="257">
@@ -8636,7 +8636,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1.01459145896</v>
+        <v>0.002201891880426743</v>
       </c>
       <c r="E257" t="n">
         <v>0</v>
@@ -8648,7 +8648,7 @@
         <v>0</v>
       </c>
       <c r="H257" t="n">
-        <v>0.3584566873954254</v>
+        <v>0.5500149835926393</v>
       </c>
     </row>
   </sheetData>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>datas/SAM_2023_64_sectors_5_households.xlsx: Accounts</t>
+          <t>datas/SHM_2023_64_sektor_5_hanehalki.xlsx: Hesaplar</t>
         </is>
       </c>
     </row>
